--- a/reports/member_funnel/downloads/member_funnel_1m_non_buyer.xlsx
+++ b/reports/member_funnel/downloads/member_funnel_1m_non_buyer.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G167"/>
+  <dimension ref="A1:G190"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,178 +468,178 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>kk_4829088785</t>
+          <t>kk_4831361074</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr">
         <is>
-          <t>303454</t>
+          <t>303574</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>(organic)</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>rkddl4</t>
+          <t>kk_4830254905</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr">
         <is>
-          <t>303596</t>
+          <t>303513</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>kk_4831842028</t>
+          <t>kk_4832204677</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr">
         <is>
-          <t>303612</t>
+          <t>303653</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>sa</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>kk_4830612400</t>
+          <t>kk_4830885654</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
-          <t>303542</t>
+          <t>303562</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>(not set)</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>kk_4830513865</t>
+          <t>kk_4831895164</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
-          <t>303529</t>
+          <t>303616</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>kk_4829077261</t>
+          <t>kk_4829516327</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
-          <t>303453</t>
+          <t>303476</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -649,68 +649,68 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>kk_4830476438</t>
+          <t>kk_4829818548</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr">
         <is>
-          <t>303525</t>
+          <t>303491</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>EFW_04</t>
+          <t>[PF]A SC_상시(1865MF,구매 장바구니)</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>kk_4831687251</t>
+          <t>kk_4831740520</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr">
         <is>
-          <t>303598</t>
+          <t>303601</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -720,25 +720,25 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>kk_4829440714</t>
+          <t>kk_4830523585</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr">
         <is>
-          <t>303471</t>
+          <t>303530</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -753,25 +753,25 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>kk_4830793813</t>
+          <t>kk_4830030364</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr">
         <is>
-          <t>303557</t>
+          <t>303499</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -781,167 +781,167 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>naversa_mo</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>charismasm74</t>
+          <t>kk_4830247238</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr">
         <is>
-          <t>303650</t>
+          <t>303510</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>(not set)</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>kk_4831500868</t>
+          <t>kk_4830591832</t>
         </is>
       </c>
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr">
         <is>
-          <t>303582</t>
+          <t>303539</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>(organic)</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>kk_4830922114</t>
+          <t>chicken0890</t>
         </is>
       </c>
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr">
         <is>
-          <t>303563</t>
+          <t>303646</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>[PF]전환_회원가입(유사)</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>hoonck1</t>
+          <t>kk_4832269209</t>
         </is>
       </c>
       <c r="B15" t="inlineStr"/>
       <c r="C15" t="inlineStr">
         <is>
-          <t>303433</t>
+          <t>303661</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>[PF]트래픽_유사+관심사</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>kk_4832205664</t>
+          <t>kk_4832293158</t>
         </is>
       </c>
       <c r="B16" t="inlineStr"/>
       <c r="C16" t="inlineStr">
         <is>
-          <t>303654</t>
+          <t>303662</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -951,25 +951,25 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>kk_4831995357</t>
+          <t>kk_4832162309</t>
         </is>
       </c>
       <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr">
         <is>
-          <t>303623</t>
+          <t>303643</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -979,195 +979,195 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>benz_running_program_2026​</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>kk_4831768959</t>
+          <t>kk_4831572710</t>
         </is>
       </c>
       <c r="B18" t="inlineStr"/>
       <c r="C18" t="inlineStr">
         <is>
-          <t>303602</t>
+          <t>303590</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>kk_4830251299</t>
+          <t>kda01126</t>
         </is>
       </c>
       <c r="B19" t="inlineStr"/>
       <c r="C19" t="inlineStr">
         <is>
-          <t>303511</t>
+          <t>303656</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>kk_4831422357</t>
+          <t>masterk</t>
         </is>
       </c>
       <c r="B20" t="inlineStr"/>
       <c r="C20" t="inlineStr">
         <is>
-          <t>303577</t>
+          <t>303524</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Official SNS</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>sa</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>kk_4831842112</t>
+          <t>kk_4832411690</t>
         </is>
       </c>
       <c r="B21" t="inlineStr"/>
       <c r="C21" t="inlineStr">
         <is>
-          <t>303613</t>
+          <t>303666</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>kk_4832105165</t>
+          <t>kk_4832425261</t>
         </is>
       </c>
       <c r="B22" t="inlineStr"/>
       <c r="C22" t="inlineStr">
         <is>
-          <t>303636</t>
+          <t>303667</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>kk_4830821550</t>
+          <t>kk_4832425669</t>
         </is>
       </c>
       <c r="B23" t="inlineStr"/>
       <c r="C23" t="inlineStr">
         <is>
-          <t>303559</t>
+          <t>303668</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1177,63 +1177,63 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>kk_4832180009</t>
+          <t>kk_4832345614</t>
         </is>
       </c>
       <c r="B24" t="inlineStr"/>
       <c r="C24" t="inlineStr">
         <is>
-          <t>303647</t>
+          <t>303664</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>kk_4831394790</t>
+          <t>kk_4831784738</t>
         </is>
       </c>
       <c r="B25" t="inlineStr"/>
       <c r="C25" t="inlineStr">
         <is>
-          <t>303575</t>
+          <t>303607</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1243,30 +1243,30 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>kk_4832023314</t>
+          <t>hotsnoopy</t>
         </is>
       </c>
       <c r="B26" t="inlineStr"/>
       <c r="C26" t="inlineStr">
         <is>
-          <t>303626</t>
+          <t>303585</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1276,30 +1276,30 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>kk_4832114535</t>
+          <t>thdud9181</t>
         </is>
       </c>
       <c r="B27" t="inlineStr"/>
       <c r="C27" t="inlineStr">
         <is>
-          <t>303637</t>
+          <t>303644</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1309,30 +1309,30 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>kk_4832248726</t>
+          <t>kk_4832310183</t>
         </is>
       </c>
       <c r="B28" t="inlineStr"/>
       <c r="C28" t="inlineStr">
         <is>
-          <t>303658</t>
+          <t>303663</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1342,30 +1342,30 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>kk_4831346086</t>
+          <t>kk_4829979824</t>
         </is>
       </c>
       <c r="B29" t="inlineStr"/>
       <c r="C29" t="inlineStr">
         <is>
-          <t>303573</t>
+          <t>303497</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1375,30 +1375,30 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>kk_4832201164</t>
+          <t>kk_4829348219</t>
         </is>
       </c>
       <c r="B30" t="inlineStr"/>
       <c r="C30" t="inlineStr">
         <is>
-          <t>303651</t>
+          <t>303468</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1408,30 +1408,30 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>kk_4832076715</t>
+          <t>kk_4831402433</t>
         </is>
       </c>
       <c r="B31" t="inlineStr"/>
       <c r="C31" t="inlineStr">
         <is>
-          <t>303629</t>
+          <t>303576</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1441,30 +1441,30 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>kk_4830767555</t>
+          <t>kk_4829294214</t>
         </is>
       </c>
       <c r="B32" t="inlineStr"/>
       <c r="C32" t="inlineStr">
         <is>
-          <t>303555</t>
+          <t>303466</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1474,228 +1474,228 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>kk_4831495694</t>
+          <t>kk_4829088785</t>
         </is>
       </c>
       <c r="B33" t="inlineStr"/>
       <c r="C33" t="inlineStr">
         <is>
-          <t>303581</t>
+          <t>303454</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>kk_4832164589</t>
+          <t>rkddl4</t>
         </is>
       </c>
       <c r="B34" t="inlineStr"/>
       <c r="C34" t="inlineStr">
         <is>
-          <t>303645</t>
+          <t>303596</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>kk_4832078505</t>
+          <t>kk_4830612400</t>
         </is>
       </c>
       <c r="B35" t="inlineStr"/>
       <c r="C35" t="inlineStr">
         <is>
-          <t>303630</t>
+          <t>303542</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>kk_4831340465</t>
+          <t>kk_4831842028</t>
         </is>
       </c>
       <c r="B36" t="inlineStr"/>
       <c r="C36" t="inlineStr">
         <is>
-          <t>303572</t>
+          <t>303612</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>jambo8</t>
+          <t>kk_4830513865</t>
         </is>
       </c>
       <c r="B37" t="inlineStr"/>
       <c r="C37" t="inlineStr">
         <is>
-          <t>303558</t>
+          <t>303529</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>kk_4832029124</t>
+          <t>kk_4829077261</t>
         </is>
       </c>
       <c r="B38" t="inlineStr"/>
       <c r="C38" t="inlineStr">
         <is>
-          <t>303627</t>
+          <t>303453</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>kk_4832100095</t>
+          <t>kk_4830476438</t>
         </is>
       </c>
       <c r="B39" t="inlineStr"/>
       <c r="C39" t="inlineStr">
         <is>
-          <t>303634</t>
+          <t>303525</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1705,96 +1705,96 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>EFW_04</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>kk_4831649243</t>
+          <t>kk_4829440714</t>
         </is>
       </c>
       <c r="B40" t="inlineStr"/>
       <c r="C40" t="inlineStr">
         <is>
-          <t>303595</t>
+          <t>303471</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>kk_4831830576</t>
+          <t>kk_4831687251</t>
         </is>
       </c>
       <c r="B41" t="inlineStr"/>
       <c r="C41" t="inlineStr">
         <is>
-          <t>303611</t>
+          <t>303598</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>kk_4832202047</t>
+          <t>kk_4830793813</t>
         </is>
       </c>
       <c r="B42" t="inlineStr"/>
       <c r="C42" t="inlineStr">
         <is>
-          <t>303652</t>
+          <t>303557</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -1804,30 +1804,30 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>saty31</t>
+          <t>charismasm74</t>
         </is>
       </c>
       <c r="B43" t="inlineStr"/>
       <c r="C43" t="inlineStr">
         <is>
-          <t>303561</t>
+          <t>303650</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -1837,30 +1837,30 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>kk_4832151833</t>
+          <t>kk_4831500868</t>
         </is>
       </c>
       <c r="B44" t="inlineStr"/>
       <c r="C44" t="inlineStr">
         <is>
-          <t>303641</t>
+          <t>303582</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -1875,25 +1875,25 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>jgj0503</t>
+          <t>kk_4830922114</t>
         </is>
       </c>
       <c r="B45" t="inlineStr"/>
       <c r="C45" t="inlineStr">
         <is>
-          <t>303605</t>
+          <t>303563</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -1903,30 +1903,30 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>[PF]전환_회원가입(유사)</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>kk_4830989652</t>
+          <t>hoonck1</t>
         </is>
       </c>
       <c r="B46" t="inlineStr"/>
       <c r="C46" t="inlineStr">
         <is>
-          <t>303569</t>
+          <t>303433</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -1936,96 +1936,96 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>[PF]트래픽_유사+관심사</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>kk_4832154317</t>
+          <t>kk_4831995357</t>
         </is>
       </c>
       <c r="B47" t="inlineStr"/>
       <c r="C47" t="inlineStr">
         <is>
-          <t>303642</t>
+          <t>303623</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>EFW</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>kk_4831536902</t>
+          <t>kk_4831768959</t>
         </is>
       </c>
       <c r="B48" t="inlineStr"/>
       <c r="C48" t="inlineStr">
         <is>
-          <t>303588</t>
+          <t>303602</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Official SNS</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>EFW_04</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>kk_4830836853</t>
+          <t>kk_4831422357</t>
         </is>
       </c>
       <c r="B49" t="inlineStr"/>
       <c r="C49" t="inlineStr">
         <is>
-          <t>303560</t>
+          <t>303577</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -2035,756 +2035,756 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>EFW_04</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>kk_4832125929</t>
+          <t>kk_4832205664</t>
         </is>
       </c>
       <c r="B50" t="inlineStr"/>
       <c r="C50" t="inlineStr">
         <is>
-          <t>303638</t>
+          <t>303654</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Official SNS</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>EFW_04</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>kk_4831850638</t>
+          <t>kk_4830251299</t>
         </is>
       </c>
       <c r="B51" t="inlineStr"/>
       <c r="C51" t="inlineStr">
         <is>
-          <t>303615</t>
+          <t>303511</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Official SNS</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>EFW_04</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>kk_4831922723</t>
+          <t>kk_4832105165</t>
         </is>
       </c>
       <c r="B52" t="inlineStr"/>
       <c r="C52" t="inlineStr">
         <is>
-          <t>303617</t>
+          <t>303636</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Official SNS</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>EFW_04</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>kk_4830778741</t>
+          <t>kk_4831842112</t>
         </is>
       </c>
       <c r="B53" t="inlineStr"/>
       <c r="C53" t="inlineStr">
         <is>
-          <t>303556</t>
+          <t>303613</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Official SNS</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>EFW_04</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>kk_4830943389</t>
+          <t>kk_4832180009</t>
         </is>
       </c>
       <c r="B54" t="inlineStr"/>
       <c r="C54" t="inlineStr">
         <is>
-          <t>303565</t>
+          <t>303647</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>(not set)</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>kk_4831612250</t>
+          <t>kk_4832114535</t>
         </is>
       </c>
       <c r="B55" t="inlineStr"/>
       <c r="C55" t="inlineStr">
         <is>
-          <t>303593</t>
+          <t>303637</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>[PF]A SC_상시(1865MF,구매 장바구니)</t>
+          <t>(not set)</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>kk_4830988405</t>
+          <t>kk_4831394790</t>
         </is>
       </c>
       <c r="B56" t="inlineStr"/>
       <c r="C56" t="inlineStr">
         <is>
-          <t>303567</t>
+          <t>303575</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>[PF]전환_상시(2565MF,비구매자)</t>
+          <t>(not set)</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>kk_4830923952</t>
+          <t>kk_4832201164</t>
         </is>
       </c>
       <c r="B57" t="inlineStr"/>
       <c r="C57" t="inlineStr">
         <is>
-          <t>303564</t>
+          <t>303651</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>[PF]전환_회원가입(유사)</t>
+          <t>(not set)</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>kk_4830963661</t>
+          <t>kk_4831346086</t>
         </is>
       </c>
       <c r="B58" t="inlineStr"/>
       <c r="C58" t="inlineStr">
         <is>
-          <t>303566</t>
+          <t>303573</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>[PF]전환_회원가입(유사)</t>
+          <t>(not set)</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>kk_4832190692</t>
+          <t>kk_4832248726</t>
         </is>
       </c>
       <c r="B59" t="inlineStr"/>
       <c r="C59" t="inlineStr">
         <is>
-          <t>303649</t>
+          <t>303658</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>(not set)</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>kk_4831997957</t>
+          <t>kk_4830821550</t>
         </is>
       </c>
       <c r="B60" t="inlineStr"/>
       <c r="C60" t="inlineStr">
         <is>
-          <t>303624</t>
+          <t>303559</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>(not set)</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>kk_4831468314</t>
+          <t>kk_4832076715</t>
         </is>
       </c>
       <c r="B61" t="inlineStr"/>
       <c r="C61" t="inlineStr">
         <is>
-          <t>303578</t>
+          <t>303629</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>(not set)</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>kk_4832001343</t>
+          <t>kk_4830767555</t>
         </is>
       </c>
       <c r="B62" t="inlineStr"/>
       <c r="C62" t="inlineStr">
         <is>
-          <t>303625</t>
+          <t>303555</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>(not set)</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>kk_4831986570</t>
+          <t>kk_4832023314</t>
         </is>
       </c>
       <c r="B63" t="inlineStr"/>
       <c r="C63" t="inlineStr">
         <is>
-          <t>303622</t>
+          <t>303626</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>(not set)</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>kk_4831799020</t>
+          <t>kk_4832164589</t>
         </is>
       </c>
       <c r="B64" t="inlineStr"/>
       <c r="C64" t="inlineStr">
         <is>
-          <t>303609</t>
+          <t>303645</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>(organic)</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>kk_4832061430</t>
+          <t>kk_4831495694</t>
         </is>
       </c>
       <c r="B65" t="inlineStr"/>
       <c r="C65" t="inlineStr">
         <is>
-          <t>303628</t>
+          <t>303581</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>(organic)</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>kk_4832100101</t>
+          <t>kk_4832078505</t>
         </is>
       </c>
       <c r="B66" t="inlineStr"/>
       <c r="C66" t="inlineStr">
         <is>
-          <t>303635</t>
+          <t>303630</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>kk_4831532519</t>
+          <t>kk_4831649243</t>
         </is>
       </c>
       <c r="B67" t="inlineStr"/>
       <c r="C67" t="inlineStr">
         <is>
-          <t>303587</t>
+          <t>303595</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>kk_4831981914</t>
+          <t>kk_4832100095</t>
         </is>
       </c>
       <c r="B68" t="inlineStr"/>
       <c r="C68" t="inlineStr">
         <is>
-          <t>303620</t>
+          <t>303634</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>kk_4831983348</t>
+          <t>kk_4832029124</t>
         </is>
       </c>
       <c r="B69" t="inlineStr"/>
       <c r="C69" t="inlineStr">
         <is>
-          <t>303621</t>
+          <t>303627</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>kk_4831502482</t>
+          <t>jambo8</t>
         </is>
       </c>
       <c r="B70" t="inlineStr"/>
       <c r="C70" t="inlineStr">
         <is>
-          <t>303583</t>
+          <t>303558</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>kk_4831257396</t>
+          <t>kk_4831340465</t>
         </is>
       </c>
       <c r="B71" t="inlineStr"/>
       <c r="C71" t="inlineStr">
         <is>
-          <t>303571</t>
+          <t>303572</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>kk_4831517271</t>
+          <t>saty31</t>
         </is>
       </c>
       <c r="B72" t="inlineStr"/>
       <c r="C72" t="inlineStr">
         <is>
-          <t>303584</t>
+          <t>303561</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -2794,30 +2794,30 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>kk_4831951614</t>
+          <t>kk_4830989652</t>
         </is>
       </c>
       <c r="B73" t="inlineStr"/>
       <c r="C73" t="inlineStr">
         <is>
-          <t>303618</t>
+          <t>303569</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -2827,30 +2827,30 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>kk_4832186210</t>
+          <t>kk_4831830576</t>
         </is>
       </c>
       <c r="B74" t="inlineStr"/>
       <c r="C74" t="inlineStr">
         <is>
-          <t>303648</t>
+          <t>303611</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -2860,30 +2860,30 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>kk_4831723596</t>
+          <t>kk_4832151833</t>
         </is>
       </c>
       <c r="B75" t="inlineStr"/>
       <c r="C75" t="inlineStr">
         <is>
-          <t>303600</t>
+          <t>303641</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -2893,30 +2893,30 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>kk_4831822425</t>
+          <t>kk_4832202047</t>
         </is>
       </c>
       <c r="B76" t="inlineStr"/>
       <c r="C76" t="inlineStr">
         <is>
-          <t>303610</t>
+          <t>303652</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -2926,30 +2926,30 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>kk_4831774426</t>
+          <t>jgj0503</t>
         </is>
       </c>
       <c r="B77" t="inlineStr"/>
       <c r="C77" t="inlineStr">
         <is>
-          <t>303604</t>
+          <t>303605</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -2959,30 +2959,30 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>kk_4831585022</t>
+          <t>kk_4832154317</t>
         </is>
       </c>
       <c r="B78" t="inlineStr"/>
       <c r="C78" t="inlineStr">
         <is>
-          <t>303591</t>
+          <t>303642</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -2992,723 +2992,723 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>EFW</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>kk_4831488942</t>
+          <t>kk_4832125929</t>
         </is>
       </c>
       <c r="B79" t="inlineStr"/>
       <c r="C79" t="inlineStr">
         <is>
-          <t>303580</t>
+          <t>303638</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Official SNS</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>EFW_04</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>minpark98</t>
+          <t>kk_4831922723</t>
         </is>
       </c>
       <c r="B80" t="inlineStr"/>
       <c r="C80" t="inlineStr">
         <is>
-          <t>303657</t>
+          <t>303617</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Official SNS</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>EFW_04</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>kk_4831615271</t>
+          <t>kk_4830778741</t>
         </is>
       </c>
       <c r="B81" t="inlineStr"/>
       <c r="C81" t="inlineStr">
         <is>
-          <t>303594</t>
+          <t>303556</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Official SNS</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>EFW_04</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>kk_4831600231</t>
+          <t>kk_4831536902</t>
         </is>
       </c>
       <c r="B82" t="inlineStr"/>
       <c r="C82" t="inlineStr">
         <is>
-          <t>303592</t>
+          <t>303588</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Official SNS</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>EFW_04</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>hotsnoopy</t>
+          <t>kk_4831850638</t>
         </is>
       </c>
       <c r="B83" t="inlineStr"/>
       <c r="C83" t="inlineStr">
         <is>
-          <t>303585</t>
+          <t>303615</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Official SNS</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>EFW_04</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>kk_4829979824</t>
+          <t>kk_4830836853</t>
         </is>
       </c>
       <c r="B84" t="inlineStr"/>
       <c r="C84" t="inlineStr">
         <is>
-          <t>303497</t>
+          <t>303560</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Official SNS</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>EFW_04</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>kk_4832310183</t>
+          <t>kk_4830943389</t>
         </is>
       </c>
       <c r="B85" t="inlineStr"/>
       <c r="C85" t="inlineStr">
         <is>
-          <t>303663</t>
+          <t>303565</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>kk_4831784738</t>
+          <t>kk_4831612250</t>
         </is>
       </c>
       <c r="B86" t="inlineStr"/>
       <c r="C86" t="inlineStr">
         <is>
-          <t>303607</t>
+          <t>303593</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>[PF]A SC_상시(1865MF,구매 장바구니)</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>kk_4829348219</t>
+          <t>kk_4830988405</t>
         </is>
       </c>
       <c r="B87" t="inlineStr"/>
       <c r="C87" t="inlineStr">
         <is>
-          <t>303468</t>
+          <t>303567</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>[PF]전환_상시(2565MF,비구매자)</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>thdud9181</t>
+          <t>kk_4830963661</t>
         </is>
       </c>
       <c r="B88" t="inlineStr"/>
       <c r="C88" t="inlineStr">
         <is>
-          <t>303644</t>
+          <t>303566</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>[PF]전환_회원가입(유사)</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>kk_4831402433</t>
+          <t>kk_4830923952</t>
         </is>
       </c>
       <c r="B89" t="inlineStr"/>
       <c r="C89" t="inlineStr">
         <is>
-          <t>303576</t>
+          <t>303564</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>[PF]전환_회원가입(유사)</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>kk_4829294214</t>
+          <t>kk_4831997957</t>
         </is>
       </c>
       <c r="B90" t="inlineStr"/>
       <c r="C90" t="inlineStr">
         <is>
-          <t>303466</t>
+          <t>303624</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>kk_4828653802</t>
+          <t>kk_4831983348</t>
         </is>
       </c>
       <c r="B91" t="inlineStr"/>
       <c r="C91" t="inlineStr">
         <is>
-          <t>303422</t>
+          <t>303621</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>kk_4829795736</t>
+          <t>kk_4831257396</t>
         </is>
       </c>
       <c r="B92" t="inlineStr"/>
       <c r="C92" t="inlineStr">
         <is>
-          <t>303489</t>
+          <t>303571</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>kk_3964942719</t>
+          <t>kk_4832100101</t>
         </is>
       </c>
       <c r="B93" t="inlineStr"/>
       <c r="C93" t="inlineStr">
         <is>
-          <t>270600</t>
+          <t>303635</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>컬럼비아_DPA_240530</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>kk_4828995903</t>
+          <t>kk_4831799020</t>
         </is>
       </c>
       <c r="B94" t="inlineStr"/>
       <c r="C94" t="inlineStr">
         <is>
-          <t>303445</t>
+          <t>303609</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>kk_4829109495</t>
+          <t>kk_4831532519</t>
         </is>
       </c>
       <c r="B95" t="inlineStr"/>
       <c r="C95" t="inlineStr">
         <is>
-          <t>303456</t>
+          <t>303587</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>da</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>kk_4830147171</t>
+          <t>kk_4831981914</t>
         </is>
       </c>
       <c r="B96" t="inlineStr"/>
       <c r="C96" t="inlineStr">
         <is>
-          <t>303506</t>
+          <t>303620</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>kk_4830615705</t>
+          <t>kk_4832190692</t>
         </is>
       </c>
       <c r="B97" t="inlineStr"/>
       <c r="C97" t="inlineStr">
         <is>
-          <t>303543</t>
+          <t>303649</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>kk_4830462005</t>
+          <t>kk_4831986570</t>
         </is>
       </c>
       <c r="B98" t="inlineStr"/>
       <c r="C98" t="inlineStr">
         <is>
-          <t>303523</t>
+          <t>303622</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>kk_4829888934</t>
+          <t>kk_4831468314</t>
         </is>
       </c>
       <c r="B99" t="inlineStr"/>
       <c r="C99" t="inlineStr">
         <is>
-          <t>303493</t>
+          <t>303578</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>EFW</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>kk_4830552074</t>
+          <t>kk_4832001343</t>
         </is>
       </c>
       <c r="B100" t="inlineStr"/>
       <c r="C100" t="inlineStr">
         <is>
-          <t>303534</t>
+          <t>303625</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -3723,25 +3723,25 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>kk_4830585310</t>
+          <t>kk_4832061430</t>
         </is>
       </c>
       <c r="B101" t="inlineStr"/>
       <c r="C101" t="inlineStr">
         <is>
-          <t>303538</t>
+          <t>303628</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -3756,58 +3756,58 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>kk_4829567584</t>
+          <t>kk_4831502482</t>
         </is>
       </c>
       <c r="B102" t="inlineStr"/>
       <c r="C102" t="inlineStr">
         <is>
-          <t>303479</t>
+          <t>303583</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>kk_4829654698</t>
+          <t>kk_4831517271</t>
         </is>
       </c>
       <c r="B103" t="inlineStr"/>
       <c r="C103" t="inlineStr">
         <is>
-          <t>303481</t>
+          <t>303584</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -3817,162 +3817,162 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>컬럼비아_DPA_240530</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>kk_4830596422</t>
+          <t>kk_4831951614</t>
         </is>
       </c>
       <c r="B104" t="inlineStr"/>
       <c r="C104" t="inlineStr">
         <is>
-          <t>303540</t>
+          <t>303618</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>kk_4830179868</t>
+          <t>kk_4832186210</t>
         </is>
       </c>
       <c r="B105" t="inlineStr"/>
       <c r="C105" t="inlineStr">
         <is>
-          <t>303508</t>
+          <t>303648</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>kk_4829899341</t>
+          <t>kk_4831774426</t>
         </is>
       </c>
       <c r="B106" t="inlineStr"/>
       <c r="C106" t="inlineStr">
         <is>
-          <t>303495</t>
+          <t>303604</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>kk_4829843383</t>
+          <t>kk_4831822425</t>
         </is>
       </c>
       <c r="B107" t="inlineStr"/>
       <c r="C107" t="inlineStr">
         <is>
-          <t>303492</t>
+          <t>303610</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>kk_4830568801</t>
+          <t>kk_4831585022</t>
         </is>
       </c>
       <c r="B108" t="inlineStr"/>
       <c r="C108" t="inlineStr">
         <is>
-          <t>303537</t>
+          <t>303591</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -3982,30 +3982,30 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>kk_4829500046</t>
+          <t>kk_4831723596</t>
         </is>
       </c>
       <c r="B109" t="inlineStr"/>
       <c r="C109" t="inlineStr">
         <is>
-          <t>303474</t>
+          <t>303600</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -4015,129 +4015,129 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>kk_4829755741</t>
+          <t>minpark98</t>
         </is>
       </c>
       <c r="B110" t="inlineStr"/>
       <c r="C110" t="inlineStr">
         <is>
-          <t>303486</t>
+          <t>303657</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>onoff</t>
+          <t>kk_4831488942</t>
         </is>
       </c>
       <c r="B111" t="inlineStr"/>
       <c r="C111" t="inlineStr">
         <is>
-          <t>303518</t>
+          <t>303580</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>kk_4829255442</t>
+          <t>kk_4831615271</t>
         </is>
       </c>
       <c r="B112" t="inlineStr"/>
       <c r="C112" t="inlineStr">
         <is>
-          <t>303464</t>
+          <t>303594</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>sa</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>kk_4830541132</t>
+          <t>kk_4831600231</t>
         </is>
       </c>
       <c r="B113" t="inlineStr"/>
       <c r="C113" t="inlineStr">
         <is>
-          <t>303533</t>
+          <t>303592</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -4147,30 +4147,30 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>sa</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>kk_4830409260</t>
+          <t>kk_4828653802</t>
         </is>
       </c>
       <c r="B114" t="inlineStr"/>
       <c r="C114" t="inlineStr">
         <is>
-          <t>303522</t>
+          <t>303422</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -4180,63 +4180,63 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>(organic)</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>kk_4829999849</t>
+          <t>kk_4829795736</t>
         </is>
       </c>
       <c r="B115" t="inlineStr"/>
       <c r="C115" t="inlineStr">
         <is>
-          <t>303498</t>
+          <t>303489</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>(not set)</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>kk_4830646394</t>
+          <t>kk_3964942719</t>
         </is>
       </c>
       <c r="B116" t="inlineStr"/>
       <c r="C116" t="inlineStr">
         <is>
-          <t>303547</t>
+          <t>270600</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -4246,63 +4246,63 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>컬럼비아_DPA_240530</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>kk_4829674741</t>
+          <t>kk_4828995903</t>
         </is>
       </c>
       <c r="B117" t="inlineStr"/>
       <c r="C117" t="inlineStr">
         <is>
-          <t>303484</t>
+          <t>303445</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>(not set)</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>kk_4830404781</t>
+          <t>kk_4829109495</t>
         </is>
       </c>
       <c r="B118" t="inlineStr"/>
       <c r="C118" t="inlineStr">
         <is>
-          <t>303521</t>
+          <t>303456</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -4312,228 +4312,228 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>da</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>kk_4830692253</t>
+          <t>kk_4830147171</t>
         </is>
       </c>
       <c r="B119" t="inlineStr"/>
       <c r="C119" t="inlineStr">
         <is>
-          <t>303550</t>
+          <t>303506</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>(not set)</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>akita1129</t>
+          <t>kk_4830615705</t>
         </is>
       </c>
       <c r="B120" t="inlineStr"/>
       <c r="C120" t="inlineStr">
         <is>
-          <t>303465</t>
+          <t>303543</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>EFW</t>
+          <t>(not set)</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>kk_4830264628</t>
+          <t>kk_4830462005</t>
         </is>
       </c>
       <c r="B121" t="inlineStr"/>
       <c r="C121" t="inlineStr">
         <is>
-          <t>303514</t>
+          <t>303523</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Official SNS</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>EFW_04</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>kk_4830559393</t>
+          <t>kk_4829888934</t>
         </is>
       </c>
       <c r="B122" t="inlineStr"/>
       <c r="C122" t="inlineStr">
         <is>
-          <t>303535</t>
+          <t>303493</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Official SNS</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>EFW_04</t>
+          <t>EFW</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>kk_4829543360</t>
+          <t>kk_4830552074</t>
         </is>
       </c>
       <c r="B123" t="inlineStr"/>
       <c r="C123" t="inlineStr">
         <is>
-          <t>303478</t>
+          <t>303534</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Official SNS</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>EFW_04</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>mong81</t>
+          <t>kk_4830585310</t>
         </is>
       </c>
       <c r="B124" t="inlineStr"/>
       <c r="C124" t="inlineStr">
         <is>
-          <t>303505</t>
+          <t>303538</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Official SNS</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>EFW_04</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>kk_4830253885</t>
+          <t>kk_4829567584</t>
         </is>
       </c>
       <c r="B125" t="inlineStr"/>
       <c r="C125" t="inlineStr">
         <is>
-          <t>303512</t>
+          <t>303479</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -4543,30 +4543,30 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0211_NEW_WOMEN</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>kk_4829512827</t>
+          <t>kk_4829654698</t>
         </is>
       </c>
       <c r="B126" t="inlineStr"/>
       <c r="C126" t="inlineStr">
         <is>
-          <t>303475</t>
+          <t>303481</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -4576,360 +4576,360 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>[PF]전환_회원가입(유사)</t>
+          <t>컬럼비아_DPA_240530</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>kk_4830637852</t>
+          <t>kk_4829843383</t>
         </is>
       </c>
       <c r="B127" t="inlineStr"/>
       <c r="C127" t="inlineStr">
         <is>
-          <t>303546</t>
+          <t>303492</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>(not set)</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>kk_4830704540</t>
+          <t>kk_4829899341</t>
         </is>
       </c>
       <c r="B128" t="inlineStr"/>
       <c r="C128" t="inlineStr">
         <is>
-          <t>303551</t>
+          <t>303495</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>(not set)</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>kk_4830308577</t>
+          <t>kk_4830596422</t>
         </is>
       </c>
       <c r="B129" t="inlineStr"/>
       <c r="C129" t="inlineStr">
         <is>
-          <t>303516</t>
+          <t>303540</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>(not set)</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>kk_4830497611</t>
+          <t>kk_4830179868</t>
         </is>
       </c>
       <c r="B130" t="inlineStr"/>
       <c r="C130" t="inlineStr">
         <is>
-          <t>303526</t>
+          <t>303508</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>(not set)</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>kk_4830722522</t>
+          <t>kk_4829500046</t>
         </is>
       </c>
       <c r="B131" t="inlineStr"/>
       <c r="C131" t="inlineStr">
         <is>
-          <t>303553</t>
+          <t>303474</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>(organic)</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>flydabi</t>
+          <t>kk_4830568801</t>
         </is>
       </c>
       <c r="B132" t="inlineStr"/>
       <c r="C132" t="inlineStr">
         <is>
-          <t>303531</t>
+          <t>303537</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>(organic)</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>kk_4830597347</t>
+          <t>kk_4829755741</t>
         </is>
       </c>
       <c r="B133" t="inlineStr"/>
       <c r="C133" t="inlineStr">
         <is>
-          <t>303541</t>
+          <t>303486</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>kk_4830659012</t>
+          <t>kk_4829255442</t>
         </is>
       </c>
       <c r="B134" t="inlineStr"/>
       <c r="C134" t="inlineStr">
         <is>
-          <t>303549</t>
+          <t>303464</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>kk_4830376206</t>
+          <t>onoff</t>
         </is>
       </c>
       <c r="B135" t="inlineStr"/>
       <c r="C135" t="inlineStr">
         <is>
-          <t>303520</t>
+          <t>303518</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>kk_4830760298</t>
+          <t>kk_4830409260</t>
         </is>
       </c>
       <c r="B136" t="inlineStr"/>
       <c r="C136" t="inlineStr">
         <is>
-          <t>303554</t>
+          <t>303522</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>benz_running_program_2026​</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>kk_4830212469</t>
+          <t>kk_4830541132</t>
         </is>
       </c>
       <c r="B137" t="inlineStr"/>
       <c r="C137" t="inlineStr">
         <is>
-          <t>303509</t>
+          <t>303533</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -4939,30 +4939,30 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>da</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>kk_4830137292</t>
+          <t>kk_4830692253</t>
         </is>
       </c>
       <c r="B138" t="inlineStr"/>
       <c r="C138" t="inlineStr">
         <is>
-          <t>303504</t>
+          <t>303550</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -4972,30 +4972,30 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>kk_4830540435</t>
+          <t>kk_4830646394</t>
         </is>
       </c>
       <c r="B139" t="inlineStr"/>
       <c r="C139" t="inlineStr">
         <is>
-          <t>303532</t>
+          <t>303547</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -5005,30 +5005,30 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>susaeg202</t>
+          <t>kk_4829674741</t>
         </is>
       </c>
       <c r="B140" t="inlineStr"/>
       <c r="C140" t="inlineStr">
         <is>
-          <t>303469</t>
+          <t>303484</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -5038,30 +5038,30 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>kk_4829761376</t>
+          <t>kk_4829999849</t>
         </is>
       </c>
       <c r="B141" t="inlineStr"/>
       <c r="C141" t="inlineStr">
         <is>
-          <t>303487</t>
+          <t>303498</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -5071,30 +5071,30 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>naversa_mo</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>kk_4830179048</t>
+          <t>kk_4830404781</t>
         </is>
       </c>
       <c r="B142" t="inlineStr"/>
       <c r="C142" t="inlineStr">
         <is>
-          <t>303507</t>
+          <t>303521</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -5104,228 +5104,228 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>naversa_mo</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>kk_4828679899</t>
+          <t>akita1129</t>
         </is>
       </c>
       <c r="B143" t="inlineStr"/>
       <c r="C143" t="inlineStr">
         <is>
-          <t>303425</t>
+          <t>303465</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Official SNS</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>EFW_04</t>
+          <t>EFW</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>kk_4828953106</t>
+          <t>kk_4829543360</t>
         </is>
       </c>
       <c r="B144" t="inlineStr"/>
       <c r="C144" t="inlineStr">
         <is>
-          <t>303440</t>
+          <t>303478</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Official SNS</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>EFW_04</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>kk_4828662042</t>
+          <t>kk_4830559393</t>
         </is>
       </c>
       <c r="B145" t="inlineStr"/>
       <c r="C145" t="inlineStr">
         <is>
-          <t>303423</t>
+          <t>303535</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Official SNS</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>EFW_04</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>kk_4828776483</t>
+          <t>mong81</t>
         </is>
       </c>
       <c r="B146" t="inlineStr"/>
       <c r="C146" t="inlineStr">
         <is>
-          <t>303428</t>
+          <t>303505</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Official SNS</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>EFW_04</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>kk_4829004394</t>
+          <t>kk_4830264628</t>
         </is>
       </c>
       <c r="B147" t="inlineStr"/>
       <c r="C147" t="inlineStr">
         <is>
-          <t>303447</t>
+          <t>303514</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Official SNS</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>EFW_04</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>kk_4828853669</t>
+          <t>kk_4830253885</t>
         </is>
       </c>
       <c r="B148" t="inlineStr"/>
       <c r="C148" t="inlineStr">
         <is>
-          <t>303431</t>
+          <t>303512</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>KAKAO_CH_MENU_0211_NEW_WOMEN</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>kk_4828870663</t>
+          <t>kk_4829512827</t>
         </is>
       </c>
       <c r="B149" t="inlineStr"/>
       <c r="C149" t="inlineStr">
         <is>
-          <t>303434</t>
+          <t>303475</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -5335,327 +5335,327 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>[PF]전환_회원가입(유사)</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>kk_4829016429</t>
+          <t>kk_4830704540</t>
         </is>
       </c>
       <c r="B150" t="inlineStr"/>
       <c r="C150" t="inlineStr">
         <is>
-          <t>303450</t>
+          <t>303551</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>kk_4829012080</t>
+          <t>kk_4830637852</t>
         </is>
       </c>
       <c r="B151" t="inlineStr"/>
       <c r="C151" t="inlineStr">
         <is>
-          <t>303448</t>
+          <t>303546</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>kk_4829143684</t>
+          <t>kk_4830497611</t>
         </is>
       </c>
       <c r="B152" t="inlineStr"/>
       <c r="C152" t="inlineStr">
         <is>
-          <t>303458</t>
+          <t>303526</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>kk_4828900771</t>
+          <t>kk_4830376206</t>
         </is>
       </c>
       <c r="B153" t="inlineStr"/>
       <c r="C153" t="inlineStr">
         <is>
-          <t>303438</t>
+          <t>303520</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>gee04171</t>
+          <t>kk_4830308577</t>
         </is>
       </c>
       <c r="B154" t="inlineStr"/>
       <c r="C154" t="inlineStr">
         <is>
-          <t>303449</t>
+          <t>303516</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>kk_4828729325</t>
+          <t>kk_4830597347</t>
         </is>
       </c>
       <c r="B155" t="inlineStr"/>
       <c r="C155" t="inlineStr">
         <is>
-          <t>303426</t>
+          <t>303541</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>EFW</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>kk_4828995176</t>
+          <t>flydabi</t>
         </is>
       </c>
       <c r="B156" t="inlineStr"/>
       <c r="C156" t="inlineStr">
         <is>
-          <t>303444</t>
+          <t>303531</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>Official SNS</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Heritage</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>kk_4828781963</t>
+          <t>kk_4830722522</t>
         </is>
       </c>
       <c r="B157" t="inlineStr"/>
       <c r="C157" t="inlineStr">
         <is>
-          <t>303429</t>
+          <t>303553</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0325_S26NEW_CTA</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>kk_4829073557</t>
+          <t>kk_4830659012</t>
         </is>
       </c>
       <c r="B158" t="inlineStr"/>
       <c r="C158" t="inlineStr">
         <is>
-          <t>303452</t>
+          <t>303549</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>[PF]전환_회원가입(유사)</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>kk_4828671248</t>
+          <t>kk_4830760298</t>
         </is>
       </c>
       <c r="B159" t="inlineStr"/>
       <c r="C159" t="inlineStr">
         <is>
-          <t>303424</t>
+          <t>303554</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -5665,129 +5665,129 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>benz_running_program_2026​</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>kk_4829107379</t>
+          <t>kk_4830212469</t>
         </is>
       </c>
       <c r="B160" t="inlineStr"/>
       <c r="C160" t="inlineStr">
         <is>
-          <t>303455</t>
+          <t>303509</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>da</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>kk_4829201314</t>
+          <t>kk_4830540435</t>
         </is>
       </c>
       <c r="B161" t="inlineStr"/>
       <c r="C161" t="inlineStr">
         <is>
-          <t>303461</t>
+          <t>303532</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>kk_4828876907</t>
+          <t>kk_4830137292</t>
         </is>
       </c>
       <c r="B162" t="inlineStr"/>
       <c r="C162" t="inlineStr">
         <is>
-          <t>303436</t>
+          <t>303504</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>kk_4828903098</t>
+          <t>susaeg202</t>
         </is>
       </c>
       <c r="B163" t="inlineStr"/>
       <c r="C163" t="inlineStr">
         <is>
-          <t>303439</t>
+          <t>303469</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -5797,30 +5797,30 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>kk_4828872529</t>
+          <t>kk_4829761376</t>
         </is>
       </c>
       <c r="B164" t="inlineStr"/>
       <c r="C164" t="inlineStr">
         <is>
-          <t>303435</t>
+          <t>303487</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -5830,30 +5830,30 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>naversa_mo</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>kk_4828987324</t>
+          <t>kk_4830179048</t>
         </is>
       </c>
       <c r="B165" t="inlineStr"/>
       <c r="C165" t="inlineStr">
         <is>
-          <t>303443</t>
+          <t>303507</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -5868,78 +5868,837 @@
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>kk_4828986759</t>
+          <t>kk_4828679899</t>
         </is>
       </c>
       <c r="B166" t="inlineStr"/>
       <c r="C166" t="inlineStr">
         <is>
-          <t>303442</t>
+          <t>303425</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Official SNS</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>naversa_mo</t>
+          <t>EFW_04</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>kyc31604</t>
+          <t>kk_4828662042</t>
         </is>
       </c>
       <c r="B167" t="inlineStr"/>
       <c r="C167" t="inlineStr">
         <is>
+          <t>303423</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>Awareness</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>benz_running_program_2026_coupon</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>kk_4828953106</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr"/>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>303440</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>Owned Channel</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>benz_running_program_2026_coupon</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>kk_4828776483</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr"/>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>303428</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>Paid Ad</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>naver_brandsearch_mobile</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>kk_4829004394</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr"/>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>303447</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>(not set)</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>kk_4829016429</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr"/>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>303450</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>Organic Traffic</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>(organic)</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>kk_4828853669</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr"/>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>303431</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>Paid Ad</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>(organic)</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>kk_4828870663</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr"/>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>303434</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>Paid Ad</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>(organic)</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>kk_4829012080</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr"/>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>303448</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>Organic Traffic</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>(referral)</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>gee04171</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr"/>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>303449</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>Paid Ad</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>6968489536332</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>kk_4829143684</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr"/>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>303458</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>Paid Ad</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>6968489536332</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>kk_4828900771</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr"/>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>303438</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>Paid Ad</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>6968489536332</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>kk_4828729325</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr"/>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>303426</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>Paid Ad</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>EFW</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>kk_4828995176</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr"/>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>303444</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>Official SNS</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>Heritage</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>kk_4828781963</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr"/>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>303429</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>Owned Channel</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>KAKAO_CH_MESSAGE_0325_S26NEW_CTA</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>kk_4829073557</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr"/>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>303452</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>Paid Ad</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>[PF]전환_회원가입(유사)</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>kk_4828671248</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr"/>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>303424</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>Awareness</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>benz_running_program_2026_coupon</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>kk_4829107379</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr"/>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>303455</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>Awareness</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>benz_running_program_2026_coupon</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>kk_4829201314</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr"/>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>303461</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>Awareness</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>benz_running_program_2026_coupon</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>kk_4828876907</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr"/>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>303436</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>Awareness</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>benz_running_program_2026_coupon</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>kk_4828872529</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr"/>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>303435</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>Paid Ad</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>naver_brandsearch_mobile</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>kk_4828903098</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr"/>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>303439</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>Paid Ad</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>naver_brandsearch_mobile</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>kk_4828987324</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr"/>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>303443</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>Paid Ad</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>naversa_mo</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>kk_4828986759</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr"/>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>303442</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>Paid Ad</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>naversa_mo</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>kyc31604</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr"/>
+      <c r="C190" t="inlineStr">
+        <is>
           <t>302496</t>
         </is>
       </c>
-      <c r="D167" t="inlineStr">
-        <is>
-          <t>Paid Ad</t>
-        </is>
-      </c>
-      <c r="E167" t="inlineStr">
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>Paid Ad</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
         <is>
           <t>sa</t>
         </is>
       </c>
-      <c r="F167" t="inlineStr">
-        <is>
-          <t>(not set)</t>
-        </is>
-      </c>
-      <c r="G167" t="inlineStr">
-        <is>
-          <t>(not set)</t>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>Unknown</t>
         </is>
       </c>
     </row>

--- a/reports/member_funnel/downloads/member_funnel_1m_non_buyer.xlsx
+++ b/reports/member_funnel/downloads/member_funnel_1m_non_buyer.xlsx
@@ -487,16 +487,8 @@
           <t>(organic)</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -520,16 +512,8 @@
           <t>naver_brandsearch_mobile</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -553,16 +537,8 @@
           <t>sa</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -581,21 +557,9 @@
           <t>Direct</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>(not set)</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -619,16 +583,8 @@
           <t>(referral)</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -652,16 +608,8 @@
           <t>naver_brandsearch_mobile</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -685,16 +633,8 @@
           <t>[PF]A SC_상시(1865MF,구매 장바구니)</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -718,16 +658,8 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -751,16 +683,8 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -784,16 +708,8 @@
           <t>naversa_mo</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -812,21 +728,9 @@
           <t>Direct</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>(not set)</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -850,16 +754,8 @@
           <t>(organic)</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -883,16 +779,8 @@
           <t>(referral)</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -916,16 +804,8 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -949,16 +829,8 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -982,16 +854,8 @@
           <t>benz_running_program_2026​</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1015,16 +879,8 @@
           <t>naver_brandsearch_mobile</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1048,16 +904,8 @@
           <t>naver_brandsearch_mobile</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1081,16 +929,8 @@
           <t>sa</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1109,21 +949,9 @@
           <t>Direct</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1142,21 +970,9 @@
           <t>Direct</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1175,21 +991,9 @@
           <t>Direct</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1208,32 +1012,20 @@
           <t>Paid Ad</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>kk_4831784738</t>
+          <t>hotsnoopy</t>
         </is>
       </c>
       <c r="B25" t="inlineStr"/>
       <c r="C25" t="inlineStr">
         <is>
-          <t>303607</t>
+          <t>303585</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1241,32 +1033,20 @@
           <t>Direct</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>hotsnoopy</t>
+          <t>kk_4829979824</t>
         </is>
       </c>
       <c r="B26" t="inlineStr"/>
       <c r="C26" t="inlineStr">
         <is>
-          <t>303585</t>
+          <t>303497</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1274,32 +1054,20 @@
           <t>Direct</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>thdud9181</t>
+          <t>kk_4831784738</t>
         </is>
       </c>
       <c r="B27" t="inlineStr"/>
       <c r="C27" t="inlineStr">
         <is>
-          <t>303644</t>
+          <t>303607</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1307,32 +1075,20 @@
           <t>Direct</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>kk_4832310183</t>
+          <t>thdud9181</t>
         </is>
       </c>
       <c r="B28" t="inlineStr"/>
       <c r="C28" t="inlineStr">
         <is>
-          <t>303663</t>
+          <t>303644</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1340,32 +1096,20 @@
           <t>Direct</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>kk_4829979824</t>
+          <t>kk_4829348219</t>
         </is>
       </c>
       <c r="B29" t="inlineStr"/>
       <c r="C29" t="inlineStr">
         <is>
-          <t>303497</t>
+          <t>303468</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1373,32 +1117,20 @@
           <t>Direct</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>kk_4829348219</t>
+          <t>kk_4831402433</t>
         </is>
       </c>
       <c r="B30" t="inlineStr"/>
       <c r="C30" t="inlineStr">
         <is>
-          <t>303468</t>
+          <t>303576</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1406,32 +1138,20 @@
           <t>Direct</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>kk_4831402433</t>
+          <t>kk_4832310183</t>
         </is>
       </c>
       <c r="B31" t="inlineStr"/>
       <c r="C31" t="inlineStr">
         <is>
-          <t>303576</t>
+          <t>303663</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1439,21 +1159,9 @@
           <t>Direct</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1472,21 +1180,9 @@
           <t>Direct</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1510,16 +1206,8 @@
           <t>6968489536332</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1543,16 +1231,8 @@
           <t>KAKAO_alimtalk</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1576,16 +1256,8 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1609,16 +1281,8 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1642,16 +1306,8 @@
           <t>naver_brandsearch_mobile</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1675,16 +1331,8 @@
           <t>6968489536332</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1708,27 +1356,19 @@
           <t>EFW_04</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>kk_4829440714</t>
+          <t>kk_4831687251</t>
         </is>
       </c>
       <c r="B40" t="inlineStr"/>
       <c r="C40" t="inlineStr">
         <is>
-          <t>303471</t>
+          <t>303598</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -1741,27 +1381,19 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>kk_4831687251</t>
+          <t>kk_4829440714</t>
         </is>
       </c>
       <c r="B41" t="inlineStr"/>
       <c r="C41" t="inlineStr">
         <is>
-          <t>303598</t>
+          <t>303471</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -1774,16 +1406,8 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1807,16 +1431,8 @@
           <t>naver_brandsearch_mobile</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1840,16 +1456,8 @@
           <t>naver_brandsearch_pc</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1873,16 +1481,8 @@
           <t>6968489536332</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F44" t="inlineStr"/>
+      <c r="G44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1906,16 +1506,8 @@
           <t>[PF]전환_회원가입(유사)</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F45" t="inlineStr"/>
+      <c r="G45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1939,16 +1531,8 @@
           <t>[PF]트래픽_유사+관심사</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F46" t="inlineStr"/>
+      <c r="G46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1972,16 +1556,8 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F47" t="inlineStr"/>
+      <c r="G47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2005,32 +1581,24 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F48" t="inlineStr"/>
+      <c r="G48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>kk_4831422357</t>
+          <t>kk_4832205664</t>
         </is>
       </c>
       <c r="B49" t="inlineStr"/>
       <c r="C49" t="inlineStr">
         <is>
-          <t>303577</t>
+          <t>303654</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Official SNS</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -2038,32 +1606,24 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F49" t="inlineStr"/>
+      <c r="G49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>kk_4832205664</t>
+          <t>kk_4830251299</t>
         </is>
       </c>
       <c r="B50" t="inlineStr"/>
       <c r="C50" t="inlineStr">
         <is>
-          <t>303654</t>
+          <t>303511</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -2071,32 +1631,24 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F50" t="inlineStr"/>
+      <c r="G50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>kk_4830251299</t>
+          <t>kk_4831422357</t>
         </is>
       </c>
       <c r="B51" t="inlineStr"/>
       <c r="C51" t="inlineStr">
         <is>
-          <t>303511</t>
+          <t>303577</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Official SNS</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -2104,16 +1656,8 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F51" t="inlineStr"/>
+      <c r="G51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2137,16 +1681,8 @@
           <t>naver_brandsearch_mobile</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F52" t="inlineStr"/>
+      <c r="G52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2170,27 +1706,19 @@
           <t>naver_brandsearch_mobile</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F53" t="inlineStr"/>
+      <c r="G53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>kk_4832180009</t>
+          <t>kk_4832076715</t>
         </is>
       </c>
       <c r="B54" t="inlineStr"/>
       <c r="C54" t="inlineStr">
         <is>
-          <t>303647</t>
+          <t>303629</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -2198,21 +1726,9 @@
           <t>Direct</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>(not set)</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="E54" t="inlineStr"/>
+      <c r="F54" t="inlineStr"/>
+      <c r="G54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2231,32 +1747,20 @@
           <t>Direct</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>(not set)</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="E55" t="inlineStr"/>
+      <c r="F55" t="inlineStr"/>
+      <c r="G55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>kk_4831394790</t>
+          <t>kk_4830821550</t>
         </is>
       </c>
       <c r="B56" t="inlineStr"/>
       <c r="C56" t="inlineStr">
         <is>
-          <t>303575</t>
+          <t>303559</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -2264,32 +1768,20 @@
           <t>Direct</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>(not set)</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="E56" t="inlineStr"/>
+      <c r="F56" t="inlineStr"/>
+      <c r="G56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>kk_4832201164</t>
+          <t>kk_4832180009</t>
         </is>
       </c>
       <c r="B57" t="inlineStr"/>
       <c r="C57" t="inlineStr">
         <is>
-          <t>303651</t>
+          <t>303647</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -2297,21 +1789,9 @@
           <t>Direct</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>(not set)</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="E57" t="inlineStr"/>
+      <c r="F57" t="inlineStr"/>
+      <c r="G57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2330,32 +1810,20 @@
           <t>Direct</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>(not set)</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="E58" t="inlineStr"/>
+      <c r="F58" t="inlineStr"/>
+      <c r="G58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>kk_4832248726</t>
+          <t>kk_4831394790</t>
         </is>
       </c>
       <c r="B59" t="inlineStr"/>
       <c r="C59" t="inlineStr">
         <is>
-          <t>303658</t>
+          <t>303575</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -2363,32 +1831,20 @@
           <t>Direct</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>(not set)</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="E59" t="inlineStr"/>
+      <c r="F59" t="inlineStr"/>
+      <c r="G59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>kk_4830821550</t>
+          <t>kk_4832201164</t>
         </is>
       </c>
       <c r="B60" t="inlineStr"/>
       <c r="C60" t="inlineStr">
         <is>
-          <t>303559</t>
+          <t>303651</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -2396,32 +1852,20 @@
           <t>Direct</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>(not set)</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="E60" t="inlineStr"/>
+      <c r="F60" t="inlineStr"/>
+      <c r="G60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>kk_4832076715</t>
+          <t>kk_4830767555</t>
         </is>
       </c>
       <c r="B61" t="inlineStr"/>
       <c r="C61" t="inlineStr">
         <is>
-          <t>303629</t>
+          <t>303555</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -2429,32 +1873,20 @@
           <t>Direct</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>(not set)</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="E61" t="inlineStr"/>
+      <c r="F61" t="inlineStr"/>
+      <c r="G61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>kk_4830767555</t>
+          <t>kk_4832248726</t>
         </is>
       </c>
       <c r="B62" t="inlineStr"/>
       <c r="C62" t="inlineStr">
         <is>
-          <t>303555</t>
+          <t>303658</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -2462,21 +1894,9 @@
           <t>Direct</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>(not set)</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="E62" t="inlineStr"/>
+      <c r="F62" t="inlineStr"/>
+      <c r="G62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -2495,37 +1915,25 @@
           <t>Direct</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>(not set)</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="E63" t="inlineStr"/>
+      <c r="F63" t="inlineStr"/>
+      <c r="G63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>kk_4832164589</t>
+          <t>kk_4831495694</t>
         </is>
       </c>
       <c r="B64" t="inlineStr"/>
       <c r="C64" t="inlineStr">
         <is>
-          <t>303645</t>
+          <t>303581</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -2533,32 +1941,24 @@
           <t>(organic)</t>
         </is>
       </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F64" t="inlineStr"/>
+      <c r="G64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>kk_4831495694</t>
+          <t>kk_4832164589</t>
         </is>
       </c>
       <c r="B65" t="inlineStr"/>
       <c r="C65" t="inlineStr">
         <is>
-          <t>303581</t>
+          <t>303645</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -2566,27 +1966,19 @@
           <t>(organic)</t>
         </is>
       </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F65" t="inlineStr"/>
+      <c r="G65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>kk_4832078505</t>
+          <t>kk_4832100095</t>
         </is>
       </c>
       <c r="B66" t="inlineStr"/>
       <c r="C66" t="inlineStr">
         <is>
-          <t>303630</t>
+          <t>303634</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -2599,27 +1991,19 @@
           <t>(referral)</t>
         </is>
       </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F66" t="inlineStr"/>
+      <c r="G66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>kk_4831649243</t>
+          <t>kk_4832078505</t>
         </is>
       </c>
       <c r="B67" t="inlineStr"/>
       <c r="C67" t="inlineStr">
         <is>
-          <t>303595</t>
+          <t>303630</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -2632,27 +2016,19 @@
           <t>(referral)</t>
         </is>
       </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F67" t="inlineStr"/>
+      <c r="G67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>kk_4832100095</t>
+          <t>kk_4831649243</t>
         </is>
       </c>
       <c r="B68" t="inlineStr"/>
       <c r="C68" t="inlineStr">
         <is>
-          <t>303634</t>
+          <t>303595</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -2665,16 +2041,8 @@
           <t>(referral)</t>
         </is>
       </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F68" t="inlineStr"/>
+      <c r="G68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -2698,16 +2066,8 @@
           <t>(referral)</t>
         </is>
       </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F69" t="inlineStr"/>
+      <c r="G69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -2731,16 +2091,8 @@
           <t>(referral)</t>
         </is>
       </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F70" t="inlineStr"/>
+      <c r="G70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -2764,27 +2116,19 @@
           <t>(referral)</t>
         </is>
       </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F71" t="inlineStr"/>
+      <c r="G71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>saty31</t>
+          <t>kk_4831830576</t>
         </is>
       </c>
       <c r="B72" t="inlineStr"/>
       <c r="C72" t="inlineStr">
         <is>
-          <t>303561</t>
+          <t>303611</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -2797,27 +2141,19 @@
           <t>6968489536332</t>
         </is>
       </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F72" t="inlineStr"/>
+      <c r="G72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>kk_4830989652</t>
+          <t>jgj0503</t>
         </is>
       </c>
       <c r="B73" t="inlineStr"/>
       <c r="C73" t="inlineStr">
         <is>
-          <t>303569</t>
+          <t>303605</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -2830,27 +2166,19 @@
           <t>6968489536332</t>
         </is>
       </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F73" t="inlineStr"/>
+      <c r="G73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>kk_4831830576</t>
+          <t>kk_4832202047</t>
         </is>
       </c>
       <c r="B74" t="inlineStr"/>
       <c r="C74" t="inlineStr">
         <is>
-          <t>303611</t>
+          <t>303652</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -2863,16 +2191,8 @@
           <t>6968489536332</t>
         </is>
       </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F74" t="inlineStr"/>
+      <c r="G74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -2896,27 +2216,19 @@
           <t>6968489536332</t>
         </is>
       </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F75" t="inlineStr"/>
+      <c r="G75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>kk_4832202047</t>
+          <t>kk_4830989652</t>
         </is>
       </c>
       <c r="B76" t="inlineStr"/>
       <c r="C76" t="inlineStr">
         <is>
-          <t>303652</t>
+          <t>303569</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -2929,27 +2241,19 @@
           <t>6968489536332</t>
         </is>
       </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F76" t="inlineStr"/>
+      <c r="G76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>jgj0503</t>
+          <t>saty31</t>
         </is>
       </c>
       <c r="B77" t="inlineStr"/>
       <c r="C77" t="inlineStr">
         <is>
-          <t>303605</t>
+          <t>303561</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -2962,16 +2266,8 @@
           <t>6968489536332</t>
         </is>
       </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F77" t="inlineStr"/>
+      <c r="G77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -2995,27 +2291,19 @@
           <t>EFW</t>
         </is>
       </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F78" t="inlineStr"/>
+      <c r="G78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>kk_4832125929</t>
+          <t>kk_4831850638</t>
         </is>
       </c>
       <c r="B79" t="inlineStr"/>
       <c r="C79" t="inlineStr">
         <is>
-          <t>303638</t>
+          <t>303615</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -3028,27 +2316,19 @@
           <t>EFW_04</t>
         </is>
       </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F79" t="inlineStr"/>
+      <c r="G79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>kk_4831922723</t>
+          <t>kk_4830778741</t>
         </is>
       </c>
       <c r="B80" t="inlineStr"/>
       <c r="C80" t="inlineStr">
         <is>
-          <t>303617</t>
+          <t>303556</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -3061,27 +2341,19 @@
           <t>EFW_04</t>
         </is>
       </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F80" t="inlineStr"/>
+      <c r="G80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>kk_4830778741</t>
+          <t>kk_4831922723</t>
         </is>
       </c>
       <c r="B81" t="inlineStr"/>
       <c r="C81" t="inlineStr">
         <is>
-          <t>303556</t>
+          <t>303617</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -3094,16 +2366,8 @@
           <t>EFW_04</t>
         </is>
       </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F81" t="inlineStr"/>
+      <c r="G81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -3127,27 +2391,19 @@
           <t>EFW_04</t>
         </is>
       </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F82" t="inlineStr"/>
+      <c r="G82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>kk_4831850638</t>
+          <t>kk_4830836853</t>
         </is>
       </c>
       <c r="B83" t="inlineStr"/>
       <c r="C83" t="inlineStr">
         <is>
-          <t>303615</t>
+          <t>303560</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -3160,27 +2416,19 @@
           <t>EFW_04</t>
         </is>
       </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F83" t="inlineStr"/>
+      <c r="G83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>kk_4830836853</t>
+          <t>kk_4832125929</t>
         </is>
       </c>
       <c r="B84" t="inlineStr"/>
       <c r="C84" t="inlineStr">
         <is>
-          <t>303560</t>
+          <t>303638</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -3193,16 +2441,8 @@
           <t>EFW_04</t>
         </is>
       </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F84" t="inlineStr"/>
+      <c r="G84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -3226,16 +2466,8 @@
           <t>KAKAO_alimtalk</t>
         </is>
       </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F85" t="inlineStr"/>
+      <c r="G85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -3259,16 +2491,8 @@
           <t>[PF]A SC_상시(1865MF,구매 장바구니)</t>
         </is>
       </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F86" t="inlineStr"/>
+      <c r="G86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -3292,27 +2516,19 @@
           <t>[PF]전환_상시(2565MF,비구매자)</t>
         </is>
       </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F87" t="inlineStr"/>
+      <c r="G87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>kk_4830963661</t>
+          <t>kk_4830923952</t>
         </is>
       </c>
       <c r="B88" t="inlineStr"/>
       <c r="C88" t="inlineStr">
         <is>
-          <t>303566</t>
+          <t>303564</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -3325,27 +2541,19 @@
           <t>[PF]전환_회원가입(유사)</t>
         </is>
       </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F88" t="inlineStr"/>
+      <c r="G88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>kk_4830923952</t>
+          <t>kk_4830963661</t>
         </is>
       </c>
       <c r="B89" t="inlineStr"/>
       <c r="C89" t="inlineStr">
         <is>
-          <t>303564</t>
+          <t>303566</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -3358,27 +2566,19 @@
           <t>[PF]전환_회원가입(유사)</t>
         </is>
       </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F89" t="inlineStr"/>
+      <c r="G89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>kk_4831997957</t>
+          <t>kk_4831799020</t>
         </is>
       </c>
       <c r="B90" t="inlineStr"/>
       <c r="C90" t="inlineStr">
         <is>
-          <t>303624</t>
+          <t>303609</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -3391,27 +2591,19 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F90" t="inlineStr"/>
+      <c r="G90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>kk_4831983348</t>
+          <t>kk_4831981914</t>
         </is>
       </c>
       <c r="B91" t="inlineStr"/>
       <c r="C91" t="inlineStr">
         <is>
-          <t>303621</t>
+          <t>303620</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -3424,27 +2616,19 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F91" t="inlineStr"/>
+      <c r="G91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>kk_4831257396</t>
+          <t>kk_4831502482</t>
         </is>
       </c>
       <c r="B92" t="inlineStr"/>
       <c r="C92" t="inlineStr">
         <is>
-          <t>303571</t>
+          <t>303583</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -3457,16 +2641,8 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F92" t="inlineStr"/>
+      <c r="G92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -3490,27 +2666,19 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F93" t="inlineStr"/>
+      <c r="G93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>kk_4831799020</t>
+          <t>kk_4831997957</t>
         </is>
       </c>
       <c r="B94" t="inlineStr"/>
       <c r="C94" t="inlineStr">
         <is>
-          <t>303609</t>
+          <t>303624</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -3523,27 +2691,19 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F94" t="inlineStr"/>
+      <c r="G94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>kk_4831532519</t>
+          <t>kk_4831983348</t>
         </is>
       </c>
       <c r="B95" t="inlineStr"/>
       <c r="C95" t="inlineStr">
         <is>
-          <t>303587</t>
+          <t>303621</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -3556,27 +2716,19 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F95" t="inlineStr"/>
+      <c r="G95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>kk_4831981914</t>
+          <t>kk_4831986570</t>
         </is>
       </c>
       <c r="B96" t="inlineStr"/>
       <c r="C96" t="inlineStr">
         <is>
-          <t>303620</t>
+          <t>303622</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -3589,27 +2741,19 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F96" t="inlineStr"/>
+      <c r="G96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>kk_4832190692</t>
+          <t>kk_4831532519</t>
         </is>
       </c>
       <c r="B97" t="inlineStr"/>
       <c r="C97" t="inlineStr">
         <is>
-          <t>303649</t>
+          <t>303587</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -3622,27 +2766,19 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F97" t="inlineStr"/>
+      <c r="G97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>kk_4831986570</t>
+          <t>kk_4832001343</t>
         </is>
       </c>
       <c r="B98" t="inlineStr"/>
       <c r="C98" t="inlineStr">
         <is>
-          <t>303622</t>
+          <t>303625</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -3655,27 +2791,19 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F98" t="inlineStr"/>
+      <c r="G98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>kk_4831468314</t>
+          <t>kk_4832061430</t>
         </is>
       </c>
       <c r="B99" t="inlineStr"/>
       <c r="C99" t="inlineStr">
         <is>
-          <t>303578</t>
+          <t>303628</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -3688,27 +2816,19 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F99" t="inlineStr"/>
+      <c r="G99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>kk_4832001343</t>
+          <t>kk_4832190692</t>
         </is>
       </c>
       <c r="B100" t="inlineStr"/>
       <c r="C100" t="inlineStr">
         <is>
-          <t>303625</t>
+          <t>303649</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -3721,27 +2841,19 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F100" t="inlineStr"/>
+      <c r="G100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>kk_4832061430</t>
+          <t>kk_4831257396</t>
         </is>
       </c>
       <c r="B101" t="inlineStr"/>
       <c r="C101" t="inlineStr">
         <is>
-          <t>303628</t>
+          <t>303571</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -3754,27 +2866,19 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F101" t="inlineStr"/>
+      <c r="G101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>kk_4831502482</t>
+          <t>kk_4831468314</t>
         </is>
       </c>
       <c r="B102" t="inlineStr"/>
       <c r="C102" t="inlineStr">
         <is>
-          <t>303583</t>
+          <t>303578</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -3787,27 +2891,19 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G102" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F102" t="inlineStr"/>
+      <c r="G102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>kk_4831517271</t>
+          <t>kk_4831951614</t>
         </is>
       </c>
       <c r="B103" t="inlineStr"/>
       <c r="C103" t="inlineStr">
         <is>
-          <t>303584</t>
+          <t>303618</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -3820,27 +2916,19 @@
           <t>naver_brandsearch_mobile</t>
         </is>
       </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F103" t="inlineStr"/>
+      <c r="G103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>kk_4831951614</t>
+          <t>kk_4832186210</t>
         </is>
       </c>
       <c r="B104" t="inlineStr"/>
       <c r="C104" t="inlineStr">
         <is>
-          <t>303618</t>
+          <t>303648</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -3853,27 +2941,19 @@
           <t>naver_brandsearch_mobile</t>
         </is>
       </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F104" t="inlineStr"/>
+      <c r="G104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>kk_4832186210</t>
+          <t>kk_4831774426</t>
         </is>
       </c>
       <c r="B105" t="inlineStr"/>
       <c r="C105" t="inlineStr">
         <is>
-          <t>303648</t>
+          <t>303604</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -3886,27 +2966,19 @@
           <t>naver_brandsearch_mobile</t>
         </is>
       </c>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G105" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F105" t="inlineStr"/>
+      <c r="G105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>kk_4831774426</t>
+          <t>kk_4831585022</t>
         </is>
       </c>
       <c r="B106" t="inlineStr"/>
       <c r="C106" t="inlineStr">
         <is>
-          <t>303604</t>
+          <t>303591</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -3919,16 +2991,8 @@
           <t>naver_brandsearch_mobile</t>
         </is>
       </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F106" t="inlineStr"/>
+      <c r="G106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -3952,27 +3016,19 @@
           <t>naver_brandsearch_mobile</t>
         </is>
       </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G107" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F107" t="inlineStr"/>
+      <c r="G107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>kk_4831585022</t>
+          <t>kk_4831517271</t>
         </is>
       </c>
       <c r="B108" t="inlineStr"/>
       <c r="C108" t="inlineStr">
         <is>
-          <t>303591</t>
+          <t>303584</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -3985,16 +3041,8 @@
           <t>naver_brandsearch_mobile</t>
         </is>
       </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G108" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F108" t="inlineStr"/>
+      <c r="G108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -4018,27 +3066,19 @@
           <t>naver_brandsearch_mobile</t>
         </is>
       </c>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G109" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F109" t="inlineStr"/>
+      <c r="G109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>minpark98</t>
+          <t>kk_4831488942</t>
         </is>
       </c>
       <c r="B110" t="inlineStr"/>
       <c r="C110" t="inlineStr">
         <is>
-          <t>303657</t>
+          <t>303580</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -4051,27 +3091,19 @@
           <t>naver_brandsearch_pc</t>
         </is>
       </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G110" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F110" t="inlineStr"/>
+      <c r="G110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>kk_4831488942</t>
+          <t>minpark98</t>
         </is>
       </c>
       <c r="B111" t="inlineStr"/>
       <c r="C111" t="inlineStr">
         <is>
-          <t>303580</t>
+          <t>303657</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -4084,27 +3116,19 @@
           <t>naver_brandsearch_pc</t>
         </is>
       </c>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G111" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F111" t="inlineStr"/>
+      <c r="G111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>kk_4831615271</t>
+          <t>kk_4831600231</t>
         </is>
       </c>
       <c r="B112" t="inlineStr"/>
       <c r="C112" t="inlineStr">
         <is>
-          <t>303594</t>
+          <t>303592</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -4117,27 +3141,19 @@
           <t>sa</t>
         </is>
       </c>
-      <c r="F112" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G112" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F112" t="inlineStr"/>
+      <c r="G112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>kk_4831600231</t>
+          <t>kk_4831615271</t>
         </is>
       </c>
       <c r="B113" t="inlineStr"/>
       <c r="C113" t="inlineStr">
         <is>
-          <t>303592</t>
+          <t>303594</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -4150,16 +3166,8 @@
           <t>sa</t>
         </is>
       </c>
-      <c r="F113" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G113" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F113" t="inlineStr"/>
+      <c r="G113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -4183,16 +3191,8 @@
           <t>(organic)</t>
         </is>
       </c>
-      <c r="F114" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G114" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F114" t="inlineStr"/>
+      <c r="G114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -4211,21 +3211,9 @@
           <t>Direct</t>
         </is>
       </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>(not set)</t>
-        </is>
-      </c>
-      <c r="F115" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G115" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="E115" t="inlineStr"/>
+      <c r="F115" t="inlineStr"/>
+      <c r="G115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -4249,16 +3237,8 @@
           <t>컬럼비아_DPA_240530</t>
         </is>
       </c>
-      <c r="F116" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G116" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F116" t="inlineStr"/>
+      <c r="G116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -4277,21 +3257,9 @@
           <t>Owned Channel</t>
         </is>
       </c>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>(not set)</t>
-        </is>
-      </c>
-      <c r="F117" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G117" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="E117" t="inlineStr"/>
+      <c r="F117" t="inlineStr"/>
+      <c r="G117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -4315,27 +3283,19 @@
           <t>da</t>
         </is>
       </c>
-      <c r="F118" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G118" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F118" t="inlineStr"/>
+      <c r="G118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>kk_4830147171</t>
+          <t>kk_4830615705</t>
         </is>
       </c>
       <c r="B119" t="inlineStr"/>
       <c r="C119" t="inlineStr">
         <is>
-          <t>303506</t>
+          <t>303543</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -4343,32 +3303,20 @@
           <t>Direct</t>
         </is>
       </c>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>(not set)</t>
-        </is>
-      </c>
-      <c r="F119" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G119" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="E119" t="inlineStr"/>
+      <c r="F119" t="inlineStr"/>
+      <c r="G119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>kk_4830615705</t>
+          <t>kk_4830147171</t>
         </is>
       </c>
       <c r="B120" t="inlineStr"/>
       <c r="C120" t="inlineStr">
         <is>
-          <t>303543</t>
+          <t>303506</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -4376,21 +3324,9 @@
           <t>Direct</t>
         </is>
       </c>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>(not set)</t>
-        </is>
-      </c>
-      <c r="F120" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G120" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="E120" t="inlineStr"/>
+      <c r="F120" t="inlineStr"/>
+      <c r="G120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -4414,16 +3350,8 @@
           <t>6968489536332</t>
         </is>
       </c>
-      <c r="F121" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G121" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F121" t="inlineStr"/>
+      <c r="G121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -4447,27 +3375,19 @@
           <t>EFW</t>
         </is>
       </c>
-      <c r="F122" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G122" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F122" t="inlineStr"/>
+      <c r="G122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>kk_4830552074</t>
+          <t>kk_4830585310</t>
         </is>
       </c>
       <c r="B123" t="inlineStr"/>
       <c r="C123" t="inlineStr">
         <is>
-          <t>303534</t>
+          <t>303538</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -4480,27 +3400,19 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F123" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G123" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F123" t="inlineStr"/>
+      <c r="G123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>kk_4830585310</t>
+          <t>kk_4830552074</t>
         </is>
       </c>
       <c r="B124" t="inlineStr"/>
       <c r="C124" t="inlineStr">
         <is>
-          <t>303538</t>
+          <t>303534</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -4513,16 +3425,8 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F124" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G124" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F124" t="inlineStr"/>
+      <c r="G124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -4546,16 +3450,8 @@
           <t>naver_brandsearch_mobile</t>
         </is>
       </c>
-      <c r="F125" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G125" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F125" t="inlineStr"/>
+      <c r="G125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -4579,16 +3475,8 @@
           <t>컬럼비아_DPA_240530</t>
         </is>
       </c>
-      <c r="F126" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G126" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F126" t="inlineStr"/>
+      <c r="G126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -4607,32 +3495,20 @@
           <t>Direct</t>
         </is>
       </c>
-      <c r="E127" t="inlineStr">
-        <is>
-          <t>(not set)</t>
-        </is>
-      </c>
-      <c r="F127" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G127" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="E127" t="inlineStr"/>
+      <c r="F127" t="inlineStr"/>
+      <c r="G127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>kk_4829899341</t>
+          <t>kk_4830596422</t>
         </is>
       </c>
       <c r="B128" t="inlineStr"/>
       <c r="C128" t="inlineStr">
         <is>
-          <t>303495</t>
+          <t>303540</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -4640,32 +3516,20 @@
           <t>Direct</t>
         </is>
       </c>
-      <c r="E128" t="inlineStr">
-        <is>
-          <t>(not set)</t>
-        </is>
-      </c>
-      <c r="F128" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G128" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="E128" t="inlineStr"/>
+      <c r="F128" t="inlineStr"/>
+      <c r="G128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>kk_4830596422</t>
+          <t>kk_4829899341</t>
         </is>
       </c>
       <c r="B129" t="inlineStr"/>
       <c r="C129" t="inlineStr">
         <is>
-          <t>303540</t>
+          <t>303495</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -4673,21 +3537,9 @@
           <t>Direct</t>
         </is>
       </c>
-      <c r="E129" t="inlineStr">
-        <is>
-          <t>(not set)</t>
-        </is>
-      </c>
-      <c r="F129" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G129" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="E129" t="inlineStr"/>
+      <c r="F129" t="inlineStr"/>
+      <c r="G129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -4706,21 +3558,9 @@
           <t>Direct</t>
         </is>
       </c>
-      <c r="E130" t="inlineStr">
-        <is>
-          <t>(not set)</t>
-        </is>
-      </c>
-      <c r="F130" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G130" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="E130" t="inlineStr"/>
+      <c r="F130" t="inlineStr"/>
+      <c r="G130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -4744,16 +3584,8 @@
           <t>(organic)</t>
         </is>
       </c>
-      <c r="F131" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G131" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F131" t="inlineStr"/>
+      <c r="G131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -4777,27 +3609,19 @@
           <t>(organic)</t>
         </is>
       </c>
-      <c r="F132" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G132" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F132" t="inlineStr"/>
+      <c r="G132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>kk_4829755741</t>
+          <t>onoff</t>
         </is>
       </c>
       <c r="B133" t="inlineStr"/>
       <c r="C133" t="inlineStr">
         <is>
-          <t>303486</t>
+          <t>303518</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -4810,16 +3634,8 @@
           <t>(referral)</t>
         </is>
       </c>
-      <c r="F133" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G133" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F133" t="inlineStr"/>
+      <c r="G133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -4843,27 +3659,19 @@
           <t>(referral)</t>
         </is>
       </c>
-      <c r="F134" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G134" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F134" t="inlineStr"/>
+      <c r="G134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>onoff</t>
+          <t>kk_4829755741</t>
         </is>
       </c>
       <c r="B135" t="inlineStr"/>
       <c r="C135" t="inlineStr">
         <is>
-          <t>303518</t>
+          <t>303486</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -4876,27 +3684,19 @@
           <t>(referral)</t>
         </is>
       </c>
-      <c r="F135" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G135" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F135" t="inlineStr"/>
+      <c r="G135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>kk_4830409260</t>
+          <t>kk_4830404781</t>
         </is>
       </c>
       <c r="B136" t="inlineStr"/>
       <c r="C136" t="inlineStr">
         <is>
-          <t>303522</t>
+          <t>303521</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -4909,27 +3709,19 @@
           <t>6968489536332</t>
         </is>
       </c>
-      <c r="F136" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G136" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F136" t="inlineStr"/>
+      <c r="G136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>kk_4830541132</t>
+          <t>kk_4830692253</t>
         </is>
       </c>
       <c r="B137" t="inlineStr"/>
       <c r="C137" t="inlineStr">
         <is>
-          <t>303533</t>
+          <t>303550</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -4942,27 +3734,19 @@
           <t>6968489536332</t>
         </is>
       </c>
-      <c r="F137" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G137" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F137" t="inlineStr"/>
+      <c r="G137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>kk_4830692253</t>
+          <t>kk_4829674741</t>
         </is>
       </c>
       <c r="B138" t="inlineStr"/>
       <c r="C138" t="inlineStr">
         <is>
-          <t>303550</t>
+          <t>303484</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -4975,27 +3759,19 @@
           <t>6968489536332</t>
         </is>
       </c>
-      <c r="F138" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G138" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F138" t="inlineStr"/>
+      <c r="G138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>kk_4830646394</t>
+          <t>kk_4830541132</t>
         </is>
       </c>
       <c r="B139" t="inlineStr"/>
       <c r="C139" t="inlineStr">
         <is>
-          <t>303547</t>
+          <t>303533</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -5008,27 +3784,19 @@
           <t>6968489536332</t>
         </is>
       </c>
-      <c r="F139" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G139" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F139" t="inlineStr"/>
+      <c r="G139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>kk_4829674741</t>
+          <t>kk_4830409260</t>
         </is>
       </c>
       <c r="B140" t="inlineStr"/>
       <c r="C140" t="inlineStr">
         <is>
-          <t>303484</t>
+          <t>303522</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -5041,27 +3809,19 @@
           <t>6968489536332</t>
         </is>
       </c>
-      <c r="F140" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G140" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F140" t="inlineStr"/>
+      <c r="G140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>kk_4829999849</t>
+          <t>kk_4830646394</t>
         </is>
       </c>
       <c r="B141" t="inlineStr"/>
       <c r="C141" t="inlineStr">
         <is>
-          <t>303498</t>
+          <t>303547</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -5074,27 +3834,19 @@
           <t>6968489536332</t>
         </is>
       </c>
-      <c r="F141" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G141" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F141" t="inlineStr"/>
+      <c r="G141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>kk_4830404781</t>
+          <t>kk_4829999849</t>
         </is>
       </c>
       <c r="B142" t="inlineStr"/>
       <c r="C142" t="inlineStr">
         <is>
-          <t>303521</t>
+          <t>303498</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -5107,16 +3859,8 @@
           <t>6968489536332</t>
         </is>
       </c>
-      <c r="F142" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G142" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F142" t="inlineStr"/>
+      <c r="G142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -5140,27 +3884,19 @@
           <t>EFW</t>
         </is>
       </c>
-      <c r="F143" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G143" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F143" t="inlineStr"/>
+      <c r="G143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>kk_4829543360</t>
+          <t>kk_4830264628</t>
         </is>
       </c>
       <c r="B144" t="inlineStr"/>
       <c r="C144" t="inlineStr">
         <is>
-          <t>303478</t>
+          <t>303514</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -5173,27 +3909,19 @@
           <t>EFW_04</t>
         </is>
       </c>
-      <c r="F144" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G144" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F144" t="inlineStr"/>
+      <c r="G144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>kk_4830559393</t>
+          <t>kk_4829543360</t>
         </is>
       </c>
       <c r="B145" t="inlineStr"/>
       <c r="C145" t="inlineStr">
         <is>
-          <t>303535</t>
+          <t>303478</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -5206,27 +3934,19 @@
           <t>EFW_04</t>
         </is>
       </c>
-      <c r="F145" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G145" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F145" t="inlineStr"/>
+      <c r="G145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>mong81</t>
+          <t>kk_4830559393</t>
         </is>
       </c>
       <c r="B146" t="inlineStr"/>
       <c r="C146" t="inlineStr">
         <is>
-          <t>303505</t>
+          <t>303535</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -5239,27 +3959,19 @@
           <t>EFW_04</t>
         </is>
       </c>
-      <c r="F146" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G146" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F146" t="inlineStr"/>
+      <c r="G146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>kk_4830264628</t>
+          <t>mong81</t>
         </is>
       </c>
       <c r="B147" t="inlineStr"/>
       <c r="C147" t="inlineStr">
         <is>
-          <t>303514</t>
+          <t>303505</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -5272,16 +3984,8 @@
           <t>EFW_04</t>
         </is>
       </c>
-      <c r="F147" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G147" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F147" t="inlineStr"/>
+      <c r="G147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -5305,16 +4009,8 @@
           <t>KAKAO_CH_MENU_0211_NEW_WOMEN</t>
         </is>
       </c>
-      <c r="F148" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G148" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F148" t="inlineStr"/>
+      <c r="G148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -5338,27 +4034,19 @@
           <t>[PF]전환_회원가입(유사)</t>
         </is>
       </c>
-      <c r="F149" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G149" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F149" t="inlineStr"/>
+      <c r="G149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>kk_4830704540</t>
+          <t>kk_4830308577</t>
         </is>
       </c>
       <c r="B150" t="inlineStr"/>
       <c r="C150" t="inlineStr">
         <is>
-          <t>303551</t>
+          <t>303516</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -5371,27 +4059,19 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F150" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G150" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F150" t="inlineStr"/>
+      <c r="G150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>kk_4830637852</t>
+          <t>kk_4830722522</t>
         </is>
       </c>
       <c r="B151" t="inlineStr"/>
       <c r="C151" t="inlineStr">
         <is>
-          <t>303546</t>
+          <t>303553</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -5404,27 +4084,19 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F151" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G151" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F151" t="inlineStr"/>
+      <c r="G151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>kk_4830497611</t>
+          <t>kk_4830704540</t>
         </is>
       </c>
       <c r="B152" t="inlineStr"/>
       <c r="C152" t="inlineStr">
         <is>
-          <t>303526</t>
+          <t>303551</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -5437,27 +4109,19 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F152" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G152" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F152" t="inlineStr"/>
+      <c r="G152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>kk_4830376206</t>
+          <t>kk_4830497611</t>
         </is>
       </c>
       <c r="B153" t="inlineStr"/>
       <c r="C153" t="inlineStr">
         <is>
-          <t>303520</t>
+          <t>303526</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -5470,27 +4134,19 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F153" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G153" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F153" t="inlineStr"/>
+      <c r="G153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>kk_4830308577</t>
+          <t>flydabi</t>
         </is>
       </c>
       <c r="B154" t="inlineStr"/>
       <c r="C154" t="inlineStr">
         <is>
-          <t>303516</t>
+          <t>303531</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -5503,27 +4159,19 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F154" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G154" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F154" t="inlineStr"/>
+      <c r="G154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>kk_4830597347</t>
+          <t>kk_4830376206</t>
         </is>
       </c>
       <c r="B155" t="inlineStr"/>
       <c r="C155" t="inlineStr">
         <is>
-          <t>303541</t>
+          <t>303520</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -5536,27 +4184,19 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F155" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G155" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F155" t="inlineStr"/>
+      <c r="G155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>flydabi</t>
+          <t>kk_4830637852</t>
         </is>
       </c>
       <c r="B156" t="inlineStr"/>
       <c r="C156" t="inlineStr">
         <is>
-          <t>303531</t>
+          <t>303546</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -5569,27 +4209,19 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F156" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G156" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F156" t="inlineStr"/>
+      <c r="G156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>kk_4830722522</t>
+          <t>kk_4830659012</t>
         </is>
       </c>
       <c r="B157" t="inlineStr"/>
       <c r="C157" t="inlineStr">
         <is>
-          <t>303553</t>
+          <t>303549</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -5602,27 +4234,19 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F157" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G157" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F157" t="inlineStr"/>
+      <c r="G157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>kk_4830659012</t>
+          <t>kk_4830597347</t>
         </is>
       </c>
       <c r="B158" t="inlineStr"/>
       <c r="C158" t="inlineStr">
         <is>
-          <t>303549</t>
+          <t>303541</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -5635,16 +4259,8 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F158" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G158" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F158" t="inlineStr"/>
+      <c r="G158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -5668,16 +4284,8 @@
           <t>benz_running_program_2026​</t>
         </is>
       </c>
-      <c r="F159" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G159" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F159" t="inlineStr"/>
+      <c r="G159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -5701,27 +4309,19 @@
           <t>da</t>
         </is>
       </c>
-      <c r="F160" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G160" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F160" t="inlineStr"/>
+      <c r="G160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>kk_4830540435</t>
+          <t>kk_4830137292</t>
         </is>
       </c>
       <c r="B161" t="inlineStr"/>
       <c r="C161" t="inlineStr">
         <is>
-          <t>303532</t>
+          <t>303504</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -5734,27 +4334,19 @@
           <t>naver_brandsearch_mobile</t>
         </is>
       </c>
-      <c r="F161" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G161" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F161" t="inlineStr"/>
+      <c r="G161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>kk_4830137292</t>
+          <t>kk_4830540435</t>
         </is>
       </c>
       <c r="B162" t="inlineStr"/>
       <c r="C162" t="inlineStr">
         <is>
-          <t>303504</t>
+          <t>303532</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -5767,16 +4359,8 @@
           <t>naver_brandsearch_mobile</t>
         </is>
       </c>
-      <c r="F162" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G162" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F162" t="inlineStr"/>
+      <c r="G162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -5800,27 +4384,19 @@
           <t>naver_brandsearch_pc</t>
         </is>
       </c>
-      <c r="F163" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G163" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F163" t="inlineStr"/>
+      <c r="G163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>kk_4829761376</t>
+          <t>kk_4830179048</t>
         </is>
       </c>
       <c r="B164" t="inlineStr"/>
       <c r="C164" t="inlineStr">
         <is>
-          <t>303487</t>
+          <t>303507</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -5833,27 +4409,19 @@
           <t>naversa_mo</t>
         </is>
       </c>
-      <c r="F164" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G164" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F164" t="inlineStr"/>
+      <c r="G164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>kk_4830179048</t>
+          <t>kk_4829761376</t>
         </is>
       </c>
       <c r="B165" t="inlineStr"/>
       <c r="C165" t="inlineStr">
         <is>
-          <t>303507</t>
+          <t>303487</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -5866,16 +4434,8 @@
           <t>naversa_mo</t>
         </is>
       </c>
-      <c r="F165" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G165" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F165" t="inlineStr"/>
+      <c r="G165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -5899,16 +4459,8 @@
           <t>EFW_04</t>
         </is>
       </c>
-      <c r="F166" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G166" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F166" t="inlineStr"/>
+      <c r="G166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -5932,16 +4484,8 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F167" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G167" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F167" t="inlineStr"/>
+      <c r="G167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -5965,16 +4509,8 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F168" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G168" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F168" t="inlineStr"/>
+      <c r="G168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -5998,16 +4534,8 @@
           <t>naver_brandsearch_mobile</t>
         </is>
       </c>
-      <c r="F169" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G169" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F169" t="inlineStr"/>
+      <c r="G169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -6026,21 +4554,9 @@
           <t>Direct</t>
         </is>
       </c>
-      <c r="E170" t="inlineStr">
-        <is>
-          <t>(not set)</t>
-        </is>
-      </c>
-      <c r="F170" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G170" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="E170" t="inlineStr"/>
+      <c r="F170" t="inlineStr"/>
+      <c r="G170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -6064,27 +4580,19 @@
           <t>(organic)</t>
         </is>
       </c>
-      <c r="F171" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G171" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F171" t="inlineStr"/>
+      <c r="G171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>kk_4828853669</t>
+          <t>kk_4828870663</t>
         </is>
       </c>
       <c r="B172" t="inlineStr"/>
       <c r="C172" t="inlineStr">
         <is>
-          <t>303431</t>
+          <t>303434</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -6097,27 +4605,19 @@
           <t>(organic)</t>
         </is>
       </c>
-      <c r="F172" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G172" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F172" t="inlineStr"/>
+      <c r="G172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>kk_4828870663</t>
+          <t>kk_4828853669</t>
         </is>
       </c>
       <c r="B173" t="inlineStr"/>
       <c r="C173" t="inlineStr">
         <is>
-          <t>303434</t>
+          <t>303431</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -6130,16 +4630,8 @@
           <t>(organic)</t>
         </is>
       </c>
-      <c r="F173" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G173" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F173" t="inlineStr"/>
+      <c r="G173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -6163,16 +4655,8 @@
           <t>(referral)</t>
         </is>
       </c>
-      <c r="F174" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G174" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F174" t="inlineStr"/>
+      <c r="G174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -6196,16 +4680,8 @@
           <t>6968489536332</t>
         </is>
       </c>
-      <c r="F175" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G175" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F175" t="inlineStr"/>
+      <c r="G175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -6229,16 +4705,8 @@
           <t>6968489536332</t>
         </is>
       </c>
-      <c r="F176" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G176" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F176" t="inlineStr"/>
+      <c r="G176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -6262,16 +4730,8 @@
           <t>6968489536332</t>
         </is>
       </c>
-      <c r="F177" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G177" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F177" t="inlineStr"/>
+      <c r="G177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -6295,16 +4755,8 @@
           <t>EFW</t>
         </is>
       </c>
-      <c r="F178" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G178" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F178" t="inlineStr"/>
+      <c r="G178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -6328,16 +4780,8 @@
           <t>Heritage</t>
         </is>
       </c>
-      <c r="F179" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G179" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F179" t="inlineStr"/>
+      <c r="G179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -6361,16 +4805,8 @@
           <t>KAKAO_CH_MESSAGE_0325_S26NEW_CTA</t>
         </is>
       </c>
-      <c r="F180" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G180" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F180" t="inlineStr"/>
+      <c r="G180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -6394,16 +4830,8 @@
           <t>[PF]전환_회원가입(유사)</t>
         </is>
       </c>
-      <c r="F181" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G181" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F181" t="inlineStr"/>
+      <c r="G181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -6427,27 +4855,19 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F182" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G182" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F182" t="inlineStr"/>
+      <c r="G182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>kk_4829107379</t>
+          <t>kk_4828876907</t>
         </is>
       </c>
       <c r="B183" t="inlineStr"/>
       <c r="C183" t="inlineStr">
         <is>
-          <t>303455</t>
+          <t>303436</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -6460,27 +4880,19 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F183" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G183" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F183" t="inlineStr"/>
+      <c r="G183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>kk_4829201314</t>
+          <t>kk_4829107379</t>
         </is>
       </c>
       <c r="B184" t="inlineStr"/>
       <c r="C184" t="inlineStr">
         <is>
-          <t>303461</t>
+          <t>303455</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -6493,27 +4905,19 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F184" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G184" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F184" t="inlineStr"/>
+      <c r="G184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>kk_4828876907</t>
+          <t>kk_4829201314</t>
         </is>
       </c>
       <c r="B185" t="inlineStr"/>
       <c r="C185" t="inlineStr">
         <is>
-          <t>303436</t>
+          <t>303461</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -6526,27 +4930,19 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F185" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G185" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F185" t="inlineStr"/>
+      <c r="G185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>kk_4828872529</t>
+          <t>kk_4828903098</t>
         </is>
       </c>
       <c r="B186" t="inlineStr"/>
       <c r="C186" t="inlineStr">
         <is>
-          <t>303435</t>
+          <t>303439</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -6559,27 +4955,19 @@
           <t>naver_brandsearch_mobile</t>
         </is>
       </c>
-      <c r="F186" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G186" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F186" t="inlineStr"/>
+      <c r="G186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>kk_4828903098</t>
+          <t>kk_4828872529</t>
         </is>
       </c>
       <c r="B187" t="inlineStr"/>
       <c r="C187" t="inlineStr">
         <is>
-          <t>303439</t>
+          <t>303435</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -6592,16 +4980,8 @@
           <t>naver_brandsearch_mobile</t>
         </is>
       </c>
-      <c r="F187" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G187" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F187" t="inlineStr"/>
+      <c r="G187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -6625,16 +5005,8 @@
           <t>naversa_mo</t>
         </is>
       </c>
-      <c r="F188" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G188" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F188" t="inlineStr"/>
+      <c r="G188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -6658,16 +5030,8 @@
           <t>naversa_mo</t>
         </is>
       </c>
-      <c r="F189" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G189" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F189" t="inlineStr"/>
+      <c r="G189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -6691,16 +5055,8 @@
           <t>sa</t>
         </is>
       </c>
-      <c r="F190" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G190" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F190" t="inlineStr"/>
+      <c r="G190" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/reports/member_funnel/downloads/member_funnel_1m_non_buyer.xlsx
+++ b/reports/member_funnel/downloads/member_funnel_1m_non_buyer.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G190"/>
+  <dimension ref="A1:F193"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,50 +456,44 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>last_category</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>top_product</t>
+          <t>purchase_product_name</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>kk_4831361074</t>
+          <t>kk_4830885654</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr">
         <is>
-          <t>303574</t>
+          <t>303562</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Official SNS</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>Official SNS</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>kk_4830254905</t>
+          <t>kk_4831895164</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr">
         <is>
-          <t>303513</t>
+          <t>303616</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -509,22 +503,21 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>kk_4832204677</t>
+          <t>ydh1184</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr">
         <is>
-          <t>303653</t>
+          <t>303696</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -534,193 +527,189 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>kk_4830885654</t>
+          <t>kk_4832961884</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
-          <t>303562</t>
+          <t>303698</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr"/>
+          <t>Owned Channel</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>(referral)</t>
+        </is>
+      </c>
       <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>kk_4831895164</t>
+          <t>kk_4832593419</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
-          <t>303616</t>
+          <t>303677</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>kk_4829516327</t>
+          <t>kk_4831740520</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
-          <t>303476</t>
+          <t>303601</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>kk_4829818548</t>
+          <t>kk_4830523585</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr">
         <is>
-          <t>303491</t>
+          <t>303530</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>[PF]A SC_상시(1865MF,구매 장바구니)</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>kk_4831740520</t>
+          <t>kk_4833676515</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr">
         <is>
-          <t>303601</t>
+          <t>303738</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>kk_4830523585</t>
+          <t>kk_4833576113</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr">
         <is>
-          <t>303530</t>
+          <t>303731</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>kk_4830030364</t>
+          <t>kk_4832799612</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr">
         <is>
-          <t>303499</t>
+          <t>303686</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>naversa_mo</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>kk_4830247238</t>
+          <t>kk_4832659421</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr">
         <is>
-          <t>303510</t>
+          <t>303680</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -728,34 +717,36 @@
           <t>Direct</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
       <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>kk_4830591832</t>
+          <t>kk_4833493849</t>
         </is>
       </c>
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr">
         <is>
-          <t>303539</t>
+          <t>303728</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -780,7 +771,6 @@
         </is>
       </c>
       <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -805,18 +795,17 @@
         </is>
       </c>
       <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>kk_4832293158</t>
+          <t>kk_4833894015</t>
         </is>
       </c>
       <c r="B16" t="inlineStr"/>
       <c r="C16" t="inlineStr">
         <is>
-          <t>303662</t>
+          <t>303761</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -830,18 +819,17 @@
         </is>
       </c>
       <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>kk_4832162309</t>
+          <t>kk_4832293158</t>
         </is>
       </c>
       <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr">
         <is>
-          <t>303643</t>
+          <t>303662</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -851,160 +839,165 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>benz_running_program_2026​</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>kk_4831572710</t>
+          <t>kk_4833753902</t>
         </is>
       </c>
       <c r="B18" t="inlineStr"/>
       <c r="C18" t="inlineStr">
         <is>
-          <t>303590</t>
+          <t>303747</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>kda01126</t>
+          <t>kk_4833855255</t>
         </is>
       </c>
       <c r="B19" t="inlineStr"/>
       <c r="C19" t="inlineStr">
         <is>
-          <t>303656</t>
+          <t>303757</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>masterk</t>
+          <t>kk_4832162309</t>
         </is>
       </c>
       <c r="B20" t="inlineStr"/>
       <c r="C20" t="inlineStr">
         <is>
-          <t>303524</t>
+          <t>303643</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>benz_running_program_2026​</t>
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>kk_4832411690</t>
+          <t>kk_4833840470</t>
         </is>
       </c>
       <c r="B21" t="inlineStr"/>
       <c r="C21" t="inlineStr">
         <is>
-          <t>303666</t>
+          <t>303756</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr"/>
+          <t>Awareness</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>benz_running_program_2026​</t>
+        </is>
+      </c>
       <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>kk_4832425261</t>
+          <t>kk_4830212469</t>
         </is>
       </c>
       <c r="B22" t="inlineStr"/>
       <c r="C22" t="inlineStr">
         <is>
-          <t>303667</t>
+          <t>303509</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr"/>
+          <t>Paid Ad</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>da</t>
+        </is>
+      </c>
       <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>kk_4832425669</t>
+          <t>kk_4833715500</t>
         </is>
       </c>
       <c r="B23" t="inlineStr"/>
       <c r="C23" t="inlineStr">
         <is>
-          <t>303668</t>
+          <t>303745</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr"/>
+          <t>Paid Ad</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>naversa_mo</t>
+        </is>
+      </c>
       <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>kk_4832345614</t>
+          <t>masterk</t>
         </is>
       </c>
       <c r="B24" t="inlineStr"/>
       <c r="C24" t="inlineStr">
         <is>
-          <t>303664</t>
+          <t>303524</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1012,20 +1005,23 @@
           <t>Paid Ad</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr"/>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>sa</t>
+        </is>
+      </c>
       <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>hotsnoopy</t>
+          <t>sjjeon1928</t>
         </is>
       </c>
       <c r="B25" t="inlineStr"/>
       <c r="C25" t="inlineStr">
         <is>
-          <t>303585</t>
+          <t>303749</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1033,20 +1029,23 @@
           <t>Direct</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr"/>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
       <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>kk_4829979824</t>
+          <t>kk_4832656308</t>
         </is>
       </c>
       <c r="B26" t="inlineStr"/>
       <c r="C26" t="inlineStr">
         <is>
-          <t>303497</t>
+          <t>303679</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1054,20 +1053,23 @@
           <t>Direct</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr"/>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
       <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>kk_4831784738</t>
+          <t>kk_4832738942</t>
         </is>
       </c>
       <c r="B27" t="inlineStr"/>
       <c r="C27" t="inlineStr">
         <is>
-          <t>303607</t>
+          <t>303683</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1075,20 +1077,23 @@
           <t>Direct</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr"/>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
       <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>thdud9181</t>
+          <t>kk_4833682381</t>
         </is>
       </c>
       <c r="B28" t="inlineStr"/>
       <c r="C28" t="inlineStr">
         <is>
-          <t>303644</t>
+          <t>303739</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1096,20 +1101,23 @@
           <t>Direct</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr"/>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
       <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>kk_4829348219</t>
+          <t>whitehole147</t>
         </is>
       </c>
       <c r="B29" t="inlineStr"/>
       <c r="C29" t="inlineStr">
         <is>
-          <t>303468</t>
+          <t>303673</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1117,20 +1125,23 @@
           <t>Direct</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr"/>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
       <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>kk_4831402433</t>
+          <t>kk_4833013784</t>
         </is>
       </c>
       <c r="B30" t="inlineStr"/>
       <c r="C30" t="inlineStr">
         <is>
-          <t>303576</t>
+          <t>303703</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1138,20 +1149,23 @@
           <t>Direct</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr"/>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
       <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>kk_4832310183</t>
+          <t>kk_4833797203</t>
         </is>
       </c>
       <c r="B31" t="inlineStr"/>
       <c r="C31" t="inlineStr">
         <is>
-          <t>303663</t>
+          <t>303750</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1159,20 +1173,23 @@
           <t>Direct</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr"/>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
       <c r="F31" t="inlineStr"/>
-      <c r="G31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>kk_4829294214</t>
+          <t>kk_4832648970</t>
         </is>
       </c>
       <c r="B32" t="inlineStr"/>
       <c r="C32" t="inlineStr">
         <is>
-          <t>303466</t>
+          <t>303678</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1180,245 +1197,239 @@
           <t>Direct</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr"/>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
       <c r="F32" t="inlineStr"/>
-      <c r="G32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>kk_4829088785</t>
+          <t>arumabc</t>
         </is>
       </c>
       <c r="B33" t="inlineStr"/>
       <c r="C33" t="inlineStr">
         <is>
-          <t>303454</t>
+          <t>303689</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="F33" t="inlineStr"/>
-      <c r="G33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>rkddl4</t>
+          <t>kk_4832411690</t>
         </is>
       </c>
       <c r="B34" t="inlineStr"/>
       <c r="C34" t="inlineStr">
         <is>
-          <t>303596</t>
+          <t>303666</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>(organic)</t>
         </is>
       </c>
       <c r="F34" t="inlineStr"/>
-      <c r="G34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>kk_4830612400</t>
+          <t>kk_4833617385</t>
         </is>
       </c>
       <c r="B35" t="inlineStr"/>
       <c r="C35" t="inlineStr">
         <is>
-          <t>303542</t>
+          <t>303734</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="F35" t="inlineStr"/>
-      <c r="G35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>kk_4831842028</t>
+          <t>kk_4833733292</t>
         </is>
       </c>
       <c r="B36" t="inlineStr"/>
       <c r="C36" t="inlineStr">
         <is>
-          <t>303612</t>
+          <t>303746</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="F36" t="inlineStr"/>
-      <c r="G36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>kk_4830513865</t>
+          <t>lily50</t>
         </is>
       </c>
       <c r="B37" t="inlineStr"/>
       <c r="C37" t="inlineStr">
         <is>
-          <t>303529</t>
+          <t>303714</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="F37" t="inlineStr"/>
-      <c r="G37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>kk_4829077261</t>
+          <t>kk_4832556634</t>
         </is>
       </c>
       <c r="B38" t="inlineStr"/>
       <c r="C38" t="inlineStr">
         <is>
-          <t>303453</t>
+          <t>303674</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="F38" t="inlineStr"/>
-      <c r="G38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>kk_4830476438</t>
+          <t>kk_4833397488</t>
         </is>
       </c>
       <c r="B39" t="inlineStr"/>
       <c r="C39" t="inlineStr">
         <is>
-          <t>303525</t>
+          <t>303723</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>EFW_04</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="F39" t="inlineStr"/>
-      <c r="G39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>kk_4831687251</t>
+          <t>kk_4833698569</t>
         </is>
       </c>
       <c r="B40" t="inlineStr"/>
       <c r="C40" t="inlineStr">
         <is>
-          <t>303598</t>
+          <t>303743</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="F40" t="inlineStr"/>
-      <c r="G40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>kk_4829440714</t>
+          <t>kk_4833115356</t>
         </is>
       </c>
       <c r="B41" t="inlineStr"/>
       <c r="C41" t="inlineStr">
         <is>
-          <t>303471</t>
+          <t>303707</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="F41" t="inlineStr"/>
-      <c r="G41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>kk_4830793813</t>
+          <t>dave1102</t>
         </is>
       </c>
       <c r="B42" t="inlineStr"/>
       <c r="C42" t="inlineStr">
         <is>
-          <t>303557</t>
+          <t>303697</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -1428,22 +1439,21 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="F42" t="inlineStr"/>
-      <c r="G42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>charismasm74</t>
+          <t>kk_4832345614</t>
         </is>
       </c>
       <c r="B43" t="inlineStr"/>
       <c r="C43" t="inlineStr">
         <is>
-          <t>303650</t>
+          <t>303664</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -1453,22 +1463,21 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="F43" t="inlineStr"/>
-      <c r="G43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>kk_4831500868</t>
+          <t>kk_4832562814</t>
         </is>
       </c>
       <c r="B44" t="inlineStr"/>
       <c r="C44" t="inlineStr">
         <is>
-          <t>303582</t>
+          <t>303675</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -1482,18 +1491,17 @@
         </is>
       </c>
       <c r="F44" t="inlineStr"/>
-      <c r="G44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>kk_4830922114</t>
+          <t>kk_4833867742</t>
         </is>
       </c>
       <c r="B45" t="inlineStr"/>
       <c r="C45" t="inlineStr">
         <is>
-          <t>303563</t>
+          <t>303760</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -1503,22 +1511,21 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>[PF]전환_회원가입(유사)</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="F45" t="inlineStr"/>
-      <c r="G45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>hoonck1</t>
+          <t>kk_4832564458</t>
         </is>
       </c>
       <c r="B46" t="inlineStr"/>
       <c r="C46" t="inlineStr">
         <is>
-          <t>303433</t>
+          <t>303676</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -1528,147 +1535,141 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>[PF]트래픽_유사+관심사</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="F46" t="inlineStr"/>
-      <c r="G46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>kk_4831995357</t>
+          <t>kk_4832425261</t>
         </is>
       </c>
       <c r="B47" t="inlineStr"/>
       <c r="C47" t="inlineStr">
         <is>
-          <t>303623</t>
+          <t>303667</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="F47" t="inlineStr"/>
-      <c r="G47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>kk_4831768959</t>
+          <t>kk_4832735078</t>
         </is>
       </c>
       <c r="B48" t="inlineStr"/>
       <c r="C48" t="inlineStr">
         <is>
-          <t>303602</t>
+          <t>303682</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="F48" t="inlineStr"/>
-      <c r="G48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>kk_4832205664</t>
+          <t>kk_4832986577</t>
         </is>
       </c>
       <c r="B49" t="inlineStr"/>
       <c r="C49" t="inlineStr">
         <is>
-          <t>303654</t>
+          <t>303701</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="F49" t="inlineStr"/>
-      <c r="G49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>kk_4830251299</t>
+          <t>wngml5609</t>
         </is>
       </c>
       <c r="B50" t="inlineStr"/>
       <c r="C50" t="inlineStr">
         <is>
-          <t>303511</t>
+          <t>303704</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="F50" t="inlineStr"/>
-      <c r="G50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>kk_4831422357</t>
+          <t>kk_4832771015</t>
         </is>
       </c>
       <c r="B51" t="inlineStr"/>
       <c r="C51" t="inlineStr">
         <is>
-          <t>303577</t>
+          <t>303685</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Official SNS</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="F51" t="inlineStr"/>
-      <c r="G51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>kk_4832105165</t>
+          <t>ckddbs4958</t>
         </is>
       </c>
       <c r="B52" t="inlineStr"/>
       <c r="C52" t="inlineStr">
         <is>
-          <t>303636</t>
+          <t>303722</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -1678,457 +1679,477 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="F52" t="inlineStr"/>
-      <c r="G52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>kk_4831842112</t>
+          <t>kk_4833234218</t>
         </is>
       </c>
       <c r="B53" t="inlineStr"/>
       <c r="C53" t="inlineStr">
         <is>
-          <t>303613</t>
+          <t>303711</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Official SNS</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>EFW_04</t>
         </is>
       </c>
       <c r="F53" t="inlineStr"/>
-      <c r="G53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>kk_4832076715</t>
+          <t>kk_4833435690</t>
         </is>
       </c>
       <c r="B54" t="inlineStr"/>
       <c r="C54" t="inlineStr">
         <is>
-          <t>303629</t>
+          <t>303726</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr"/>
+          <t>Official SNS</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>EFW_04</t>
+        </is>
+      </c>
       <c r="F54" t="inlineStr"/>
-      <c r="G54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>kk_4832114535</t>
+          <t>kk_4833215714</t>
         </is>
       </c>
       <c r="B55" t="inlineStr"/>
       <c r="C55" t="inlineStr">
         <is>
-          <t>303637</t>
+          <t>303709</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr"/>
+          <t>Official SNS</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>EFW_04</t>
+        </is>
+      </c>
       <c r="F55" t="inlineStr"/>
-      <c r="G55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>kk_4830821550</t>
+          <t>kk_4832874454</t>
         </is>
       </c>
       <c r="B56" t="inlineStr"/>
       <c r="C56" t="inlineStr">
         <is>
-          <t>303559</t>
+          <t>303691</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr"/>
+          <t>Official SNS</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>EFW_04</t>
+        </is>
+      </c>
       <c r="F56" t="inlineStr"/>
-      <c r="G56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>kk_4832180009</t>
+          <t>kk_4833692238</t>
         </is>
       </c>
       <c r="B57" t="inlineStr"/>
       <c r="C57" t="inlineStr">
         <is>
-          <t>303647</t>
+          <t>303741</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr"/>
+          <t>Paid Ad</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>[PF]전환_회원가입(유사)</t>
+        </is>
+      </c>
       <c r="F57" t="inlineStr"/>
-      <c r="G57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>kk_4831346086</t>
+          <t>kk_4833915167</t>
         </is>
       </c>
       <c r="B58" t="inlineStr"/>
       <c r="C58" t="inlineStr">
         <is>
-          <t>303573</t>
+          <t>303764</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr"/>
+          <t>Paid Ad</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>[PF]트래픽_유사+관심사</t>
+        </is>
+      </c>
       <c r="F58" t="inlineStr"/>
-      <c r="G58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>kk_4831394790</t>
+          <t>kk_4833289287</t>
         </is>
       </c>
       <c r="B59" t="inlineStr"/>
       <c r="C59" t="inlineStr">
         <is>
-          <t>303575</t>
+          <t>303716</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr"/>
+          <t>Awareness</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>benz_running_program_2026_coupon</t>
+        </is>
+      </c>
       <c r="F59" t="inlineStr"/>
-      <c r="G59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>kk_4832201164</t>
+          <t>kk_4833588305</t>
         </is>
       </c>
       <c r="B60" t="inlineStr"/>
       <c r="C60" t="inlineStr">
         <is>
-          <t>303651</t>
+          <t>303733</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr"/>
+          <t>Awareness</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>benz_running_program_2026_coupon</t>
+        </is>
+      </c>
       <c r="F60" t="inlineStr"/>
-      <c r="G60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>kk_4830767555</t>
+          <t>kk_4833858368</t>
         </is>
       </c>
       <c r="B61" t="inlineStr"/>
       <c r="C61" t="inlineStr">
         <is>
-          <t>303555</t>
+          <t>303758</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr"/>
+          <t>Awareness</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>benz_running_program_2026_coupon</t>
+        </is>
+      </c>
       <c r="F61" t="inlineStr"/>
-      <c r="G61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>kk_4832248726</t>
+          <t>kk_4833937502</t>
         </is>
       </c>
       <c r="B62" t="inlineStr"/>
       <c r="C62" t="inlineStr">
         <is>
-          <t>303658</t>
+          <t>303767</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr"/>
+          <t>Awareness</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>benz_running_program_2026_coupon</t>
+        </is>
+      </c>
       <c r="F62" t="inlineStr"/>
-      <c r="G62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>kk_4832023314</t>
+          <t>kk_4832963009</t>
         </is>
       </c>
       <c r="B63" t="inlineStr"/>
       <c r="C63" t="inlineStr">
         <is>
-          <t>303626</t>
+          <t>303699</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr"/>
+          <t>Awareness</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>benz_running_program_2026_coupon</t>
+        </is>
+      </c>
       <c r="F63" t="inlineStr"/>
-      <c r="G63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>kk_4831495694</t>
+          <t>kk_4832497383</t>
         </is>
       </c>
       <c r="B64" t="inlineStr"/>
       <c r="C64" t="inlineStr">
         <is>
-          <t>303581</t>
+          <t>303669</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="F64" t="inlineStr"/>
-      <c r="G64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>kk_4832164589</t>
+          <t>kk_4833788564</t>
         </is>
       </c>
       <c r="B65" t="inlineStr"/>
       <c r="C65" t="inlineStr">
         <is>
-          <t>303645</t>
+          <t>303748</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>benz_running_program_2026​</t>
         </is>
       </c>
       <c r="F65" t="inlineStr"/>
-      <c r="G65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>kk_4832100095</t>
+          <t>hlpt10</t>
         </is>
       </c>
       <c r="B66" t="inlineStr"/>
       <c r="C66" t="inlineStr">
         <is>
-          <t>303634</t>
+          <t>303715</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="F66" t="inlineStr"/>
-      <c r="G66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>kk_4832078505</t>
+          <t>kk_4832855902</t>
         </is>
       </c>
       <c r="B67" t="inlineStr"/>
       <c r="C67" t="inlineStr">
         <is>
-          <t>303630</t>
+          <t>303690</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="F67" t="inlineStr"/>
-      <c r="G67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>kk_4831649243</t>
+          <t>kk_4832804456</t>
         </is>
       </c>
       <c r="B68" t="inlineStr"/>
       <c r="C68" t="inlineStr">
         <is>
-          <t>303595</t>
+          <t>303687</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="F68" t="inlineStr"/>
-      <c r="G68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>kk_4832029124</t>
+          <t>kk_4832888908</t>
         </is>
       </c>
       <c r="B69" t="inlineStr"/>
       <c r="C69" t="inlineStr">
         <is>
-          <t>303627</t>
+          <t>303693</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="F69" t="inlineStr"/>
-      <c r="G69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>jambo8</t>
+          <t>mystyle1999</t>
         </is>
       </c>
       <c r="B70" t="inlineStr"/>
       <c r="C70" t="inlineStr">
         <is>
-          <t>303558</t>
+          <t>303695</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="F70" t="inlineStr"/>
-      <c r="G70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>kk_4831340465</t>
+          <t>kk_4832527479</t>
         </is>
       </c>
       <c r="B71" t="inlineStr"/>
       <c r="C71" t="inlineStr">
         <is>
-          <t>303572</t>
+          <t>303672</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
       <c r="F71" t="inlineStr"/>
-      <c r="G71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>kk_4831830576</t>
+          <t>kk_4832745335</t>
         </is>
       </c>
       <c r="B72" t="inlineStr"/>
       <c r="C72" t="inlineStr">
         <is>
-          <t>303611</t>
+          <t>303684</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -2138,22 +2159,21 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
       <c r="F72" t="inlineStr"/>
-      <c r="G72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>jgj0503</t>
+          <t>jinchoi24</t>
         </is>
       </c>
       <c r="B73" t="inlineStr"/>
       <c r="C73" t="inlineStr">
         <is>
-          <t>303605</t>
+          <t>303754</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -2163,22 +2183,21 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
       <c r="F73" t="inlineStr"/>
-      <c r="G73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>kk_4832202047</t>
+          <t>kk_4832811973</t>
         </is>
       </c>
       <c r="B74" t="inlineStr"/>
       <c r="C74" t="inlineStr">
         <is>
-          <t>303652</t>
+          <t>303688</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -2188,22 +2207,21 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>naversa_mo</t>
         </is>
       </c>
       <c r="F74" t="inlineStr"/>
-      <c r="G74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>kk_4832151833</t>
+          <t>kk_4833676329</t>
         </is>
       </c>
       <c r="B75" t="inlineStr"/>
       <c r="C75" t="inlineStr">
         <is>
-          <t>303641</t>
+          <t>303737</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -2213,22 +2231,21 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>sa</t>
         </is>
       </c>
       <c r="F75" t="inlineStr"/>
-      <c r="G75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>kk_4830989652</t>
+          <t>kk_4833836842</t>
         </is>
       </c>
       <c r="B76" t="inlineStr"/>
       <c r="C76" t="inlineStr">
         <is>
-          <t>303569</t>
+          <t>303753</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -2238,397 +2255,381 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>sa</t>
         </is>
       </c>
       <c r="F76" t="inlineStr"/>
-      <c r="G76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>saty31</t>
+          <t>hotsnoopy</t>
         </is>
       </c>
       <c r="B77" t="inlineStr"/>
       <c r="C77" t="inlineStr">
         <is>
-          <t>303561</t>
+          <t>303585</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="F77" t="inlineStr"/>
-      <c r="G77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>kk_4832154317</t>
+          <t>thdud9181</t>
         </is>
       </c>
       <c r="B78" t="inlineStr"/>
       <c r="C78" t="inlineStr">
         <is>
-          <t>303642</t>
+          <t>303644</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>EFW</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="F78" t="inlineStr"/>
-      <c r="G78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>kk_4831850638</t>
+          <t>kk_4831402433</t>
         </is>
       </c>
       <c r="B79" t="inlineStr"/>
       <c r="C79" t="inlineStr">
         <is>
-          <t>303615</t>
+          <t>303576</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Official SNS</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>EFW_04</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="F79" t="inlineStr"/>
-      <c r="G79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>kk_4830778741</t>
+          <t>kk_4833961109</t>
         </is>
       </c>
       <c r="B80" t="inlineStr"/>
       <c r="C80" t="inlineStr">
         <is>
-          <t>303556</t>
+          <t>303770</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Official SNS</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>EFW_04</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="F80" t="inlineStr"/>
-      <c r="G80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>kk_4831922723</t>
+          <t>kk_4833294708</t>
         </is>
       </c>
       <c r="B81" t="inlineStr"/>
       <c r="C81" t="inlineStr">
         <is>
-          <t>303617</t>
+          <t>303717</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Official SNS</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>EFW_04</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="F81" t="inlineStr"/>
-      <c r="G81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>kk_4831536902</t>
+          <t>kk_4831784738</t>
         </is>
       </c>
       <c r="B82" t="inlineStr"/>
       <c r="C82" t="inlineStr">
         <is>
-          <t>303588</t>
+          <t>303607</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Official SNS</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>EFW_04</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="F82" t="inlineStr"/>
-      <c r="G82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>kk_4830836853</t>
+          <t>kk_4833706874</t>
         </is>
       </c>
       <c r="B83" t="inlineStr"/>
       <c r="C83" t="inlineStr">
         <is>
-          <t>303560</t>
+          <t>303744</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Official SNS</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>EFW_04</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="F83" t="inlineStr"/>
-      <c r="G83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>kk_4832125929</t>
+          <t>kk_4832310183</t>
         </is>
       </c>
       <c r="B84" t="inlineStr"/>
       <c r="C84" t="inlineStr">
         <is>
-          <t>303638</t>
+          <t>303663</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Official SNS</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>EFW_04</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="F84" t="inlineStr"/>
-      <c r="G84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>kk_4830943389</t>
+          <t>kk_4833232918</t>
         </is>
       </c>
       <c r="B85" t="inlineStr"/>
       <c r="C85" t="inlineStr">
         <is>
-          <t>303565</t>
+          <t>303710</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="F85" t="inlineStr"/>
-      <c r="G85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>kk_4831612250</t>
+          <t>pjj1758</t>
         </is>
       </c>
       <c r="B86" t="inlineStr"/>
       <c r="C86" t="inlineStr">
         <is>
-          <t>303593</t>
+          <t>303708</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>[PF]A SC_상시(1865MF,구매 장바구니)</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="F86" t="inlineStr"/>
-      <c r="G86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>kk_4830988405</t>
+          <t>rkddl4</t>
         </is>
       </c>
       <c r="B87" t="inlineStr"/>
       <c r="C87" t="inlineStr">
         <is>
-          <t>303567</t>
+          <t>303596</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>[PF]전환_상시(2565MF,비구매자)</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="F87" t="inlineStr"/>
-      <c r="G87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>kk_4830923952</t>
+          <t>kk_4830612400</t>
         </is>
       </c>
       <c r="B88" t="inlineStr"/>
       <c r="C88" t="inlineStr">
         <is>
-          <t>303564</t>
+          <t>303542</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>[PF]전환_회원가입(유사)</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="F88" t="inlineStr"/>
-      <c r="G88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>kk_4830963661</t>
+          <t>kk_4831842028</t>
         </is>
       </c>
       <c r="B89" t="inlineStr"/>
       <c r="C89" t="inlineStr">
         <is>
-          <t>303566</t>
+          <t>303612</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>[PF]전환_회원가입(유사)</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="F89" t="inlineStr"/>
-      <c r="G89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>kk_4831799020</t>
+          <t>kk_4830513865</t>
         </is>
       </c>
       <c r="B90" t="inlineStr"/>
       <c r="C90" t="inlineStr">
         <is>
-          <t>303609</t>
+          <t>303529</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="F90" t="inlineStr"/>
-      <c r="G90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>kk_4831981914</t>
+          <t>kk_4830476438</t>
         </is>
       </c>
       <c r="B91" t="inlineStr"/>
       <c r="C91" t="inlineStr">
         <is>
-          <t>303620</t>
+          <t>303525</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>EFW_04</t>
         </is>
       </c>
       <c r="F91" t="inlineStr"/>
-      <c r="G91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>kk_4831502482</t>
+          <t>kk_4831687251</t>
         </is>
       </c>
       <c r="B92" t="inlineStr"/>
       <c r="C92" t="inlineStr">
         <is>
-          <t>303583</t>
+          <t>303598</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -2642,123 +2643,118 @@
         </is>
       </c>
       <c r="F92" t="inlineStr"/>
-      <c r="G92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>kk_4832100101</t>
+          <t>kk_4830793813</t>
         </is>
       </c>
       <c r="B93" t="inlineStr"/>
       <c r="C93" t="inlineStr">
         <is>
-          <t>303635</t>
+          <t>303557</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="F93" t="inlineStr"/>
-      <c r="G93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>kk_4831997957</t>
+          <t>charismasm74</t>
         </is>
       </c>
       <c r="B94" t="inlineStr"/>
       <c r="C94" t="inlineStr">
         <is>
-          <t>303624</t>
+          <t>303650</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
       <c r="F94" t="inlineStr"/>
-      <c r="G94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>kk_4831983348</t>
+          <t>kk_4831500868</t>
         </is>
       </c>
       <c r="B95" t="inlineStr"/>
       <c r="C95" t="inlineStr">
         <is>
-          <t>303621</t>
+          <t>303582</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="F95" t="inlineStr"/>
-      <c r="G95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>kk_4831986570</t>
+          <t>kk_4830922114</t>
         </is>
       </c>
       <c r="B96" t="inlineStr"/>
       <c r="C96" t="inlineStr">
         <is>
-          <t>303622</t>
+          <t>303563</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>[PF]전환_회원가입(유사)</t>
         </is>
       </c>
       <c r="F96" t="inlineStr"/>
-      <c r="G96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>kk_4831532519</t>
+          <t>kk_4832205664</t>
         </is>
       </c>
       <c r="B97" t="inlineStr"/>
       <c r="C97" t="inlineStr">
         <is>
-          <t>303587</t>
+          <t>303654</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -2767,18 +2763,17 @@
         </is>
       </c>
       <c r="F97" t="inlineStr"/>
-      <c r="G97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>kk_4832001343</t>
+          <t>kk_4831995357</t>
         </is>
       </c>
       <c r="B98" t="inlineStr"/>
       <c r="C98" t="inlineStr">
         <is>
-          <t>303625</t>
+          <t>303623</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -2792,18 +2787,17 @@
         </is>
       </c>
       <c r="F98" t="inlineStr"/>
-      <c r="G98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>kk_4832061430</t>
+          <t>kk_4831768959</t>
         </is>
       </c>
       <c r="B99" t="inlineStr"/>
       <c r="C99" t="inlineStr">
         <is>
-          <t>303628</t>
+          <t>303602</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -2817,23 +2811,22 @@
         </is>
       </c>
       <c r="F99" t="inlineStr"/>
-      <c r="G99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>kk_4832190692</t>
+          <t>kk_4831422357</t>
         </is>
       </c>
       <c r="B100" t="inlineStr"/>
       <c r="C100" t="inlineStr">
         <is>
-          <t>303649</t>
+          <t>303577</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Official SNS</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -2842,18 +2835,17 @@
         </is>
       </c>
       <c r="F100" t="inlineStr"/>
-      <c r="G100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>kk_4831257396</t>
+          <t>kk_4830251299</t>
         </is>
       </c>
       <c r="B101" t="inlineStr"/>
       <c r="C101" t="inlineStr">
         <is>
-          <t>303571</t>
+          <t>303511</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -2867,43 +2859,41 @@
         </is>
       </c>
       <c r="F101" t="inlineStr"/>
-      <c r="G101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>kk_4831468314</t>
+          <t>kk_4832105165</t>
         </is>
       </c>
       <c r="B102" t="inlineStr"/>
       <c r="C102" t="inlineStr">
         <is>
-          <t>303578</t>
+          <t>303636</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="F102" t="inlineStr"/>
-      <c r="G102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>kk_4831951614</t>
+          <t>kk_4831842112</t>
         </is>
       </c>
       <c r="B103" t="inlineStr"/>
       <c r="C103" t="inlineStr">
         <is>
-          <t>303618</t>
+          <t>303613</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -2917,268 +2907,257 @@
         </is>
       </c>
       <c r="F103" t="inlineStr"/>
-      <c r="G103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>kk_4832186210</t>
+          <t>kk_4830767555</t>
         </is>
       </c>
       <c r="B104" t="inlineStr"/>
       <c r="C104" t="inlineStr">
         <is>
-          <t>303648</t>
+          <t>303555</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="F104" t="inlineStr"/>
-      <c r="G104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>kk_4831774426</t>
+          <t>kk_4832248726</t>
         </is>
       </c>
       <c r="B105" t="inlineStr"/>
       <c r="C105" t="inlineStr">
         <is>
-          <t>303604</t>
+          <t>303658</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="F105" t="inlineStr"/>
-      <c r="G105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>kk_4831585022</t>
+          <t>kk_4831346086</t>
         </is>
       </c>
       <c r="B106" t="inlineStr"/>
       <c r="C106" t="inlineStr">
         <is>
-          <t>303591</t>
+          <t>303573</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="F106" t="inlineStr"/>
-      <c r="G106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>kk_4831822425</t>
+          <t>kk_4832180009</t>
         </is>
       </c>
       <c r="B107" t="inlineStr"/>
       <c r="C107" t="inlineStr">
         <is>
-          <t>303610</t>
+          <t>303647</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="F107" t="inlineStr"/>
-      <c r="G107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>kk_4831517271</t>
+          <t>kk_4831394790</t>
         </is>
       </c>
       <c r="B108" t="inlineStr"/>
       <c r="C108" t="inlineStr">
         <is>
-          <t>303584</t>
+          <t>303575</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="F108" t="inlineStr"/>
-      <c r="G108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>kk_4831723596</t>
+          <t>kk_4832023314</t>
         </is>
       </c>
       <c r="B109" t="inlineStr"/>
       <c r="C109" t="inlineStr">
         <is>
-          <t>303600</t>
+          <t>303626</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="F109" t="inlineStr"/>
-      <c r="G109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>kk_4831488942</t>
+          <t>kk_4830821550</t>
         </is>
       </c>
       <c r="B110" t="inlineStr"/>
       <c r="C110" t="inlineStr">
         <is>
-          <t>303580</t>
+          <t>303559</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="F110" t="inlineStr"/>
-      <c r="G110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>minpark98</t>
+          <t>kk_4832114535</t>
         </is>
       </c>
       <c r="B111" t="inlineStr"/>
       <c r="C111" t="inlineStr">
         <is>
-          <t>303657</t>
+          <t>303637</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="F111" t="inlineStr"/>
-      <c r="G111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>kk_4831600231</t>
+          <t>kk_4832076715</t>
         </is>
       </c>
       <c r="B112" t="inlineStr"/>
       <c r="C112" t="inlineStr">
         <is>
-          <t>303592</t>
+          <t>303629</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="F112" t="inlineStr"/>
-      <c r="G112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>kk_4831615271</t>
+          <t>kk_4832201164</t>
         </is>
       </c>
       <c r="B113" t="inlineStr"/>
       <c r="C113" t="inlineStr">
         <is>
-          <t>303594</t>
+          <t>303651</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="F113" t="inlineStr"/>
-      <c r="G113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>kk_4828653802</t>
+          <t>kk_4832164589</t>
         </is>
       </c>
       <c r="B114" t="inlineStr"/>
       <c r="C114" t="inlineStr">
         <is>
-          <t>303422</t>
+          <t>303645</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -3192,177 +3171,185 @@
         </is>
       </c>
       <c r="F114" t="inlineStr"/>
-      <c r="G114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>kk_4829795736</t>
+          <t>kk_4831495694</t>
         </is>
       </c>
       <c r="B115" t="inlineStr"/>
       <c r="C115" t="inlineStr">
         <is>
-          <t>303489</t>
+          <t>303581</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E115" t="inlineStr"/>
+          <t>Organic Traffic</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>(organic)</t>
+        </is>
+      </c>
       <c r="F115" t="inlineStr"/>
-      <c r="G115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>kk_3964942719</t>
+          <t>kk_4831649243</t>
         </is>
       </c>
       <c r="B116" t="inlineStr"/>
       <c r="C116" t="inlineStr">
         <is>
-          <t>270600</t>
+          <t>303595</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>컬럼비아_DPA_240530</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="F116" t="inlineStr"/>
-      <c r="G116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>kk_4828995903</t>
+          <t>kk_4832078505</t>
         </is>
       </c>
       <c r="B117" t="inlineStr"/>
       <c r="C117" t="inlineStr">
         <is>
-          <t>303445</t>
+          <t>303630</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
-        </is>
-      </c>
-      <c r="E117" t="inlineStr"/>
+          <t>Organic Traffic</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>(referral)</t>
+        </is>
+      </c>
       <c r="F117" t="inlineStr"/>
-      <c r="G117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>kk_4829109495</t>
+          <t>kk_4831340465</t>
         </is>
       </c>
       <c r="B118" t="inlineStr"/>
       <c r="C118" t="inlineStr">
         <is>
-          <t>303456</t>
+          <t>303572</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>da</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="F118" t="inlineStr"/>
-      <c r="G118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>kk_4830615705</t>
+          <t>kk_4832100095</t>
         </is>
       </c>
       <c r="B119" t="inlineStr"/>
       <c r="C119" t="inlineStr">
         <is>
-          <t>303543</t>
+          <t>303634</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E119" t="inlineStr"/>
+          <t>Organic Traffic</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>(referral)</t>
+        </is>
+      </c>
       <c r="F119" t="inlineStr"/>
-      <c r="G119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>kk_4830147171</t>
+          <t>kk_4832029124</t>
         </is>
       </c>
       <c r="B120" t="inlineStr"/>
       <c r="C120" t="inlineStr">
         <is>
-          <t>303506</t>
+          <t>303627</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E120" t="inlineStr"/>
+          <t>Organic Traffic</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>(referral)</t>
+        </is>
+      </c>
       <c r="F120" t="inlineStr"/>
-      <c r="G120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>kk_4830462005</t>
+          <t>jambo8</t>
         </is>
       </c>
       <c r="B121" t="inlineStr"/>
       <c r="C121" t="inlineStr">
         <is>
-          <t>303523</t>
+          <t>303558</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="F121" t="inlineStr"/>
-      <c r="G121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>kk_4829888934</t>
+          <t>kk_4832151833</t>
         </is>
       </c>
       <c r="B122" t="inlineStr"/>
       <c r="C122" t="inlineStr">
         <is>
-          <t>303493</t>
+          <t>303641</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -3372,97 +3359,93 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>EFW</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="F122" t="inlineStr"/>
-      <c r="G122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>kk_4830585310</t>
+          <t>kk_4832202047</t>
         </is>
       </c>
       <c r="B123" t="inlineStr"/>
       <c r="C123" t="inlineStr">
         <is>
-          <t>303538</t>
+          <t>303652</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="F123" t="inlineStr"/>
-      <c r="G123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>kk_4830552074</t>
+          <t>kk_4831830576</t>
         </is>
       </c>
       <c r="B124" t="inlineStr"/>
       <c r="C124" t="inlineStr">
         <is>
-          <t>303534</t>
+          <t>303611</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="F124" t="inlineStr"/>
-      <c r="G124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>kk_4829567584</t>
+          <t>saty31</t>
         </is>
       </c>
       <c r="B125" t="inlineStr"/>
       <c r="C125" t="inlineStr">
         <is>
-          <t>303479</t>
+          <t>303561</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="F125" t="inlineStr"/>
-      <c r="G125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>kk_4829654698</t>
+          <t>jgj0503</t>
         </is>
       </c>
       <c r="B126" t="inlineStr"/>
       <c r="C126" t="inlineStr">
         <is>
-          <t>303481</t>
+          <t>303605</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -3472,231 +3455,237 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>컬럼비아_DPA_240530</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="F126" t="inlineStr"/>
-      <c r="G126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>kk_4829843383</t>
+          <t>kk_4830989652</t>
         </is>
       </c>
       <c r="B127" t="inlineStr"/>
       <c r="C127" t="inlineStr">
         <is>
-          <t>303492</t>
+          <t>303569</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E127" t="inlineStr"/>
+          <t>Paid Ad</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>6968489536332</t>
+        </is>
+      </c>
       <c r="F127" t="inlineStr"/>
-      <c r="G127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>kk_4830596422</t>
+          <t>kk_4832154317</t>
         </is>
       </c>
       <c r="B128" t="inlineStr"/>
       <c r="C128" t="inlineStr">
         <is>
-          <t>303540</t>
+          <t>303642</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E128" t="inlineStr"/>
+          <t>Paid Ad</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>EFW</t>
+        </is>
+      </c>
       <c r="F128" t="inlineStr"/>
-      <c r="G128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>kk_4829899341</t>
+          <t>kk_4831922723</t>
         </is>
       </c>
       <c r="B129" t="inlineStr"/>
       <c r="C129" t="inlineStr">
         <is>
-          <t>303495</t>
+          <t>303617</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E129" t="inlineStr"/>
+          <t>Official SNS</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>EFW_04</t>
+        </is>
+      </c>
       <c r="F129" t="inlineStr"/>
-      <c r="G129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>kk_4830179868</t>
+          <t>kk_4832125929</t>
         </is>
       </c>
       <c r="B130" t="inlineStr"/>
       <c r="C130" t="inlineStr">
         <is>
-          <t>303508</t>
+          <t>303638</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E130" t="inlineStr"/>
+          <t>Official SNS</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>EFW_04</t>
+        </is>
+      </c>
       <c r="F130" t="inlineStr"/>
-      <c r="G130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>kk_4829500046</t>
+          <t>kk_4830836853</t>
         </is>
       </c>
       <c r="B131" t="inlineStr"/>
       <c r="C131" t="inlineStr">
         <is>
-          <t>303474</t>
+          <t>303560</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Official SNS</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>EFW_04</t>
         </is>
       </c>
       <c r="F131" t="inlineStr"/>
-      <c r="G131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>kk_4830568801</t>
+          <t>kk_4831850638</t>
         </is>
       </c>
       <c r="B132" t="inlineStr"/>
       <c r="C132" t="inlineStr">
         <is>
-          <t>303537</t>
+          <t>303615</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Official SNS</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>EFW_04</t>
         </is>
       </c>
       <c r="F132" t="inlineStr"/>
-      <c r="G132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>onoff</t>
+          <t>kk_4830778741</t>
         </is>
       </c>
       <c r="B133" t="inlineStr"/>
       <c r="C133" t="inlineStr">
         <is>
-          <t>303518</t>
+          <t>303556</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Official SNS</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>EFW_04</t>
         </is>
       </c>
       <c r="F133" t="inlineStr"/>
-      <c r="G133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>kk_4829255442</t>
+          <t>kk_4830943389</t>
         </is>
       </c>
       <c r="B134" t="inlineStr"/>
       <c r="C134" t="inlineStr">
         <is>
-          <t>303464</t>
+          <t>303565</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="F134" t="inlineStr"/>
-      <c r="G134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>kk_4829755741</t>
+          <t>kk_4831612250</t>
         </is>
       </c>
       <c r="B135" t="inlineStr"/>
       <c r="C135" t="inlineStr">
         <is>
-          <t>303486</t>
+          <t>303593</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>[PF]A SC_상시(1865MF,구매 장바구니)</t>
         </is>
       </c>
       <c r="F135" t="inlineStr"/>
-      <c r="G135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>kk_4830404781</t>
+          <t>kk_4830988405</t>
         </is>
       </c>
       <c r="B136" t="inlineStr"/>
       <c r="C136" t="inlineStr">
         <is>
-          <t>303521</t>
+          <t>303567</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -3706,322 +3695,309 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>[PF]전환_상시(2565MF,비구매자)</t>
         </is>
       </c>
       <c r="F136" t="inlineStr"/>
-      <c r="G136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>kk_4830692253</t>
+          <t>kk_4831532519</t>
         </is>
       </c>
       <c r="B137" t="inlineStr"/>
       <c r="C137" t="inlineStr">
         <is>
-          <t>303550</t>
+          <t>303587</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="F137" t="inlineStr"/>
-      <c r="G137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>kk_4829674741</t>
+          <t>kk_4831986570</t>
         </is>
       </c>
       <c r="B138" t="inlineStr"/>
       <c r="C138" t="inlineStr">
         <is>
-          <t>303484</t>
+          <t>303622</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="F138" t="inlineStr"/>
-      <c r="G138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>kk_4830541132</t>
+          <t>kk_4832100101</t>
         </is>
       </c>
       <c r="B139" t="inlineStr"/>
       <c r="C139" t="inlineStr">
         <is>
-          <t>303533</t>
+          <t>303635</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="F139" t="inlineStr"/>
-      <c r="G139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>kk_4830409260</t>
+          <t>kk_4831981914</t>
         </is>
       </c>
       <c r="B140" t="inlineStr"/>
       <c r="C140" t="inlineStr">
         <is>
-          <t>303522</t>
+          <t>303620</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="F140" t="inlineStr"/>
-      <c r="G140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>kk_4830646394</t>
+          <t>kk_4831799020</t>
         </is>
       </c>
       <c r="B141" t="inlineStr"/>
       <c r="C141" t="inlineStr">
         <is>
-          <t>303547</t>
+          <t>303609</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="F141" t="inlineStr"/>
-      <c r="G141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>kk_4829999849</t>
+          <t>kk_4831983348</t>
         </is>
       </c>
       <c r="B142" t="inlineStr"/>
       <c r="C142" t="inlineStr">
         <is>
-          <t>303498</t>
+          <t>303621</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="F142" t="inlineStr"/>
-      <c r="G142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>akita1129</t>
+          <t>kk_4832061430</t>
         </is>
       </c>
       <c r="B143" t="inlineStr"/>
       <c r="C143" t="inlineStr">
         <is>
-          <t>303465</t>
+          <t>303628</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>EFW</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="F143" t="inlineStr"/>
-      <c r="G143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>kk_4830264628</t>
+          <t>kk_4832001343</t>
         </is>
       </c>
       <c r="B144" t="inlineStr"/>
       <c r="C144" t="inlineStr">
         <is>
-          <t>303514</t>
+          <t>303625</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Official SNS</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>EFW_04</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="F144" t="inlineStr"/>
-      <c r="G144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>kk_4829543360</t>
+          <t>kk_4831502482</t>
         </is>
       </c>
       <c r="B145" t="inlineStr"/>
       <c r="C145" t="inlineStr">
         <is>
-          <t>303478</t>
+          <t>303583</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Official SNS</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>EFW_04</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="F145" t="inlineStr"/>
-      <c r="G145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>kk_4830559393</t>
+          <t>kk_4831257396</t>
         </is>
       </c>
       <c r="B146" t="inlineStr"/>
       <c r="C146" t="inlineStr">
         <is>
-          <t>303535</t>
+          <t>303571</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Official SNS</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>EFW_04</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="F146" t="inlineStr"/>
-      <c r="G146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>mong81</t>
+          <t>kk_4832190692</t>
         </is>
       </c>
       <c r="B147" t="inlineStr"/>
       <c r="C147" t="inlineStr">
         <is>
-          <t>303505</t>
+          <t>303649</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>Official SNS</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>EFW_04</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="F147" t="inlineStr"/>
-      <c r="G147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>kk_4830253885</t>
+          <t>kk_4831997957</t>
         </is>
       </c>
       <c r="B148" t="inlineStr"/>
       <c r="C148" t="inlineStr">
         <is>
-          <t>303512</t>
+          <t>303624</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0211_NEW_WOMEN</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="F148" t="inlineStr"/>
-      <c r="G148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>kk_4829512827</t>
+          <t>kk_4832186210</t>
         </is>
       </c>
       <c r="B149" t="inlineStr"/>
       <c r="C149" t="inlineStr">
         <is>
-          <t>303475</t>
+          <t>303648</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -4031,272 +4007,261 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>[PF]전환_회원가입(유사)</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="F149" t="inlineStr"/>
-      <c r="G149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>kk_4830308577</t>
+          <t>kk_4831774426</t>
         </is>
       </c>
       <c r="B150" t="inlineStr"/>
       <c r="C150" t="inlineStr">
         <is>
-          <t>303516</t>
+          <t>303604</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="F150" t="inlineStr"/>
-      <c r="G150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>kk_4830722522</t>
+          <t>kk_4831822425</t>
         </is>
       </c>
       <c r="B151" t="inlineStr"/>
       <c r="C151" t="inlineStr">
         <is>
-          <t>303553</t>
+          <t>303610</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="F151" t="inlineStr"/>
-      <c r="G151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>kk_4830704540</t>
+          <t>kk_4831723596</t>
         </is>
       </c>
       <c r="B152" t="inlineStr"/>
       <c r="C152" t="inlineStr">
         <is>
-          <t>303551</t>
+          <t>303600</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="F152" t="inlineStr"/>
-      <c r="G152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>kk_4830497611</t>
+          <t>kk_4831951614</t>
         </is>
       </c>
       <c r="B153" t="inlineStr"/>
       <c r="C153" t="inlineStr">
         <is>
-          <t>303526</t>
+          <t>303618</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="F153" t="inlineStr"/>
-      <c r="G153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>flydabi</t>
+          <t>kk_4831585022</t>
         </is>
       </c>
       <c r="B154" t="inlineStr"/>
       <c r="C154" t="inlineStr">
         <is>
-          <t>303531</t>
+          <t>303591</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="F154" t="inlineStr"/>
-      <c r="G154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>kk_4830376206</t>
+          <t>kk_4831517271</t>
         </is>
       </c>
       <c r="B155" t="inlineStr"/>
       <c r="C155" t="inlineStr">
         <is>
-          <t>303520</t>
+          <t>303584</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="F155" t="inlineStr"/>
-      <c r="G155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>kk_4830637852</t>
+          <t>minpark98</t>
         </is>
       </c>
       <c r="B156" t="inlineStr"/>
       <c r="C156" t="inlineStr">
         <is>
-          <t>303546</t>
+          <t>303657</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
       <c r="F156" t="inlineStr"/>
-      <c r="G156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>kk_4830659012</t>
+          <t>kk_4831488942</t>
         </is>
       </c>
       <c r="B157" t="inlineStr"/>
       <c r="C157" t="inlineStr">
         <is>
-          <t>303549</t>
+          <t>303580</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
       <c r="F157" t="inlineStr"/>
-      <c r="G157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>kk_4830597347</t>
+          <t>kk_4831615271</t>
         </is>
       </c>
       <c r="B158" t="inlineStr"/>
       <c r="C158" t="inlineStr">
         <is>
-          <t>303541</t>
+          <t>303594</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>sa</t>
         </is>
       </c>
       <c r="F158" t="inlineStr"/>
-      <c r="G158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>kk_4830760298</t>
+          <t>kk_4831600231</t>
         </is>
       </c>
       <c r="B159" t="inlineStr"/>
       <c r="C159" t="inlineStr">
         <is>
-          <t>303554</t>
+          <t>303592</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>benz_running_program_2026​</t>
+          <t>sa</t>
         </is>
       </c>
       <c r="F159" t="inlineStr"/>
-      <c r="G159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>kk_4830212469</t>
+          <t>kk_3964942719</t>
         </is>
       </c>
       <c r="B160" t="inlineStr"/>
       <c r="C160" t="inlineStr">
         <is>
-          <t>303509</t>
+          <t>270600</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -4306,72 +4271,69 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>da</t>
+          <t>컬럼비아_DPA_240530</t>
         </is>
       </c>
       <c r="F160" t="inlineStr"/>
-      <c r="G160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>kk_4830137292</t>
+          <t>kk_4830147171</t>
         </is>
       </c>
       <c r="B161" t="inlineStr"/>
       <c r="C161" t="inlineStr">
         <is>
-          <t>303504</t>
+          <t>303506</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="F161" t="inlineStr"/>
-      <c r="G161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>kk_4830540435</t>
+          <t>kk_4830615705</t>
         </is>
       </c>
       <c r="B162" t="inlineStr"/>
       <c r="C162" t="inlineStr">
         <is>
-          <t>303532</t>
+          <t>303543</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="F162" t="inlineStr"/>
-      <c r="G162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>susaeg202</t>
+          <t>kk_4830462005</t>
         </is>
       </c>
       <c r="B163" t="inlineStr"/>
       <c r="C163" t="inlineStr">
         <is>
-          <t>303469</t>
+          <t>303523</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -4381,218 +4343,213 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="F163" t="inlineStr"/>
-      <c r="G163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>kk_4830179048</t>
+          <t>kk_4830552074</t>
         </is>
       </c>
       <c r="B164" t="inlineStr"/>
       <c r="C164" t="inlineStr">
         <is>
-          <t>303507</t>
+          <t>303534</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>naversa_mo</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="F164" t="inlineStr"/>
-      <c r="G164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>kk_4829761376</t>
+          <t>kk_4830585310</t>
         </is>
       </c>
       <c r="B165" t="inlineStr"/>
       <c r="C165" t="inlineStr">
         <is>
-          <t>303487</t>
+          <t>303538</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>naversa_mo</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="F165" t="inlineStr"/>
-      <c r="G165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>kk_4828679899</t>
+          <t>kk_4830179868</t>
         </is>
       </c>
       <c r="B166" t="inlineStr"/>
       <c r="C166" t="inlineStr">
         <is>
-          <t>303425</t>
+          <t>303508</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>Official SNS</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>EFW_04</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="F166" t="inlineStr"/>
-      <c r="G166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>kk_4828662042</t>
+          <t>kk_4830596422</t>
         </is>
       </c>
       <c r="B167" t="inlineStr"/>
       <c r="C167" t="inlineStr">
         <is>
-          <t>303423</t>
+          <t>303540</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="F167" t="inlineStr"/>
-      <c r="G167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>kk_4828953106</t>
+          <t>kk_4830568801</t>
         </is>
       </c>
       <c r="B168" t="inlineStr"/>
       <c r="C168" t="inlineStr">
         <is>
-          <t>303440</t>
+          <t>303537</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>(organic)</t>
         </is>
       </c>
       <c r="F168" t="inlineStr"/>
-      <c r="G168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>kk_4828776483</t>
+          <t>onoff</t>
         </is>
       </c>
       <c r="B169" t="inlineStr"/>
       <c r="C169" t="inlineStr">
         <is>
-          <t>303428</t>
+          <t>303518</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="F169" t="inlineStr"/>
-      <c r="G169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>kk_4829004394</t>
+          <t>kk_4829999849</t>
         </is>
       </c>
       <c r="B170" t="inlineStr"/>
       <c r="C170" t="inlineStr">
         <is>
-          <t>303447</t>
+          <t>303498</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E170" t="inlineStr"/>
+          <t>Paid Ad</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>6968489536332</t>
+        </is>
+      </c>
       <c r="F170" t="inlineStr"/>
-      <c r="G170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>kk_4829016429</t>
+          <t>kk_4830692253</t>
         </is>
       </c>
       <c r="B171" t="inlineStr"/>
       <c r="C171" t="inlineStr">
         <is>
-          <t>303450</t>
+          <t>303550</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="F171" t="inlineStr"/>
-      <c r="G171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>kk_4828870663</t>
+          <t>kk_4830409260</t>
         </is>
       </c>
       <c r="B172" t="inlineStr"/>
       <c r="C172" t="inlineStr">
         <is>
-          <t>303434</t>
+          <t>303522</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -4602,22 +4559,21 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="F172" t="inlineStr"/>
-      <c r="G172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>kk_4828853669</t>
+          <t>kk_4830404781</t>
         </is>
       </c>
       <c r="B173" t="inlineStr"/>
       <c r="C173" t="inlineStr">
         <is>
-          <t>303431</t>
+          <t>303521</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -4627,47 +4583,45 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="F173" t="inlineStr"/>
-      <c r="G173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>kk_4829012080</t>
+          <t>kk_4830646394</t>
         </is>
       </c>
       <c r="B174" t="inlineStr"/>
       <c r="C174" t="inlineStr">
         <is>
-          <t>303448</t>
+          <t>303547</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="F174" t="inlineStr"/>
-      <c r="G174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>gee04171</t>
+          <t>kk_4830541132</t>
         </is>
       </c>
       <c r="B175" t="inlineStr"/>
       <c r="C175" t="inlineStr">
         <is>
-          <t>303449</t>
+          <t>303533</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -4681,168 +4635,161 @@
         </is>
       </c>
       <c r="F175" t="inlineStr"/>
-      <c r="G175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>kk_4829143684</t>
+          <t>kk_4830559393</t>
         </is>
       </c>
       <c r="B176" t="inlineStr"/>
       <c r="C176" t="inlineStr">
         <is>
-          <t>303458</t>
+          <t>303535</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Official SNS</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>EFW_04</t>
         </is>
       </c>
       <c r="F176" t="inlineStr"/>
-      <c r="G176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>kk_4828900771</t>
+          <t>mong81</t>
         </is>
       </c>
       <c r="B177" t="inlineStr"/>
       <c r="C177" t="inlineStr">
         <is>
-          <t>303438</t>
+          <t>303505</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Official SNS</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>EFW_04</t>
         </is>
       </c>
       <c r="F177" t="inlineStr"/>
-      <c r="G177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>kk_4828729325</t>
+          <t>kk_4830264628</t>
         </is>
       </c>
       <c r="B178" t="inlineStr"/>
       <c r="C178" t="inlineStr">
         <is>
-          <t>303426</t>
+          <t>303514</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Official SNS</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>EFW</t>
+          <t>EFW_04</t>
         </is>
       </c>
       <c r="F178" t="inlineStr"/>
-      <c r="G178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>kk_4828995176</t>
+          <t>kk_4830253885</t>
         </is>
       </c>
       <c r="B179" t="inlineStr"/>
       <c r="C179" t="inlineStr">
         <is>
-          <t>303444</t>
+          <t>303512</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>Official SNS</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Heritage</t>
+          <t>KAKAO_CH_MENU_0211_NEW_WOMEN</t>
         </is>
       </c>
       <c r="F179" t="inlineStr"/>
-      <c r="G179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>kk_4828781963</t>
+          <t>kk_4830704540</t>
         </is>
       </c>
       <c r="B180" t="inlineStr"/>
       <c r="C180" t="inlineStr">
         <is>
-          <t>303429</t>
+          <t>303551</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0325_S26NEW_CTA</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="F180" t="inlineStr"/>
-      <c r="G180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>kk_4829073557</t>
+          <t>kk_4830497611</t>
         </is>
       </c>
       <c r="B181" t="inlineStr"/>
       <c r="C181" t="inlineStr">
         <is>
-          <t>303452</t>
+          <t>303526</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>[PF]전환_회원가입(유사)</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="F181" t="inlineStr"/>
-      <c r="G181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>kk_4828671248</t>
+          <t>kk_4830637852</t>
         </is>
       </c>
       <c r="B182" t="inlineStr"/>
       <c r="C182" t="inlineStr">
         <is>
-          <t>303424</t>
+          <t>303546</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -4856,18 +4803,17 @@
         </is>
       </c>
       <c r="F182" t="inlineStr"/>
-      <c r="G182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>kk_4828876907</t>
+          <t>kk_4830597347</t>
         </is>
       </c>
       <c r="B183" t="inlineStr"/>
       <c r="C183" t="inlineStr">
         <is>
-          <t>303436</t>
+          <t>303541</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -4881,18 +4827,17 @@
         </is>
       </c>
       <c r="F183" t="inlineStr"/>
-      <c r="G183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>kk_4829107379</t>
+          <t>flydabi</t>
         </is>
       </c>
       <c r="B184" t="inlineStr"/>
       <c r="C184" t="inlineStr">
         <is>
-          <t>303455</t>
+          <t>303531</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -4906,18 +4851,17 @@
         </is>
       </c>
       <c r="F184" t="inlineStr"/>
-      <c r="G184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>kk_4829201314</t>
+          <t>kk_4830376206</t>
         </is>
       </c>
       <c r="B185" t="inlineStr"/>
       <c r="C185" t="inlineStr">
         <is>
-          <t>303461</t>
+          <t>303520</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -4931,132 +4875,198 @@
         </is>
       </c>
       <c r="F185" t="inlineStr"/>
-      <c r="G185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>kk_4828903098</t>
+          <t>kk_4830308577</t>
         </is>
       </c>
       <c r="B186" t="inlineStr"/>
       <c r="C186" t="inlineStr">
         <is>
-          <t>303439</t>
+          <t>303516</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="F186" t="inlineStr"/>
-      <c r="G186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>kk_4828872529</t>
+          <t>kk_4830659012</t>
         </is>
       </c>
       <c r="B187" t="inlineStr"/>
       <c r="C187" t="inlineStr">
         <is>
-          <t>303435</t>
+          <t>303549</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="F187" t="inlineStr"/>
-      <c r="G187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>kk_4828987324</t>
+          <t>kk_4830722522</t>
         </is>
       </c>
       <c r="B188" t="inlineStr"/>
       <c r="C188" t="inlineStr">
         <is>
-          <t>303443</t>
+          <t>303553</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>naversa_mo</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="F188" t="inlineStr"/>
-      <c r="G188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>kk_4828986759</t>
+          <t>kk_4830760298</t>
         </is>
       </c>
       <c r="B189" t="inlineStr"/>
       <c r="C189" t="inlineStr">
         <is>
-          <t>303442</t>
+          <t>303554</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>naversa_mo</t>
+          <t>benz_running_program_2026​</t>
         </is>
       </c>
       <c r="F189" t="inlineStr"/>
-      <c r="G189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>kyc31604</t>
+          <t>kk_4830137292</t>
         </is>
       </c>
       <c r="B190" t="inlineStr"/>
       <c r="C190" t="inlineStr">
         <is>
+          <t>303504</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>Paid Ad</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>naver_brandsearch_mobile</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr"/>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>kk_4830540435</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr"/>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>303532</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>Paid Ad</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>naver_brandsearch_mobile</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr"/>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>kk_4830179048</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr"/>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>303507</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>Paid Ad</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>naversa_mo</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr"/>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>kyc31604</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr"/>
+      <c r="C193" t="inlineStr">
+        <is>
           <t>302496</t>
         </is>
       </c>
-      <c r="D190" t="inlineStr">
-        <is>
-          <t>Paid Ad</t>
-        </is>
-      </c>
-      <c r="E190" t="inlineStr">
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>Paid Ad</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
         <is>
           <t>sa</t>
         </is>
       </c>
-      <c r="F190" t="inlineStr"/>
-      <c r="G190" t="inlineStr"/>
+      <c r="F193" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/reports/member_funnel/downloads/member_funnel_1m_non_buyer.xlsx
+++ b/reports/member_funnel/downloads/member_funnel_1m_non_buyer.xlsx
@@ -799,13 +799,13 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>kk_4833894015</t>
+          <t>kk_4833753902</t>
         </is>
       </c>
       <c r="B16" t="inlineStr"/>
       <c r="C16" t="inlineStr">
         <is>
-          <t>303761</t>
+          <t>303747</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -847,13 +847,13 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>kk_4833753902</t>
+          <t>kk_4833894015</t>
         </is>
       </c>
       <c r="B18" t="inlineStr"/>
       <c r="C18" t="inlineStr">
         <is>
-          <t>303747</t>
+          <t>303761</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1039,13 +1039,13 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>kk_4832656308</t>
+          <t>kk_4832648970</t>
         </is>
       </c>
       <c r="B26" t="inlineStr"/>
       <c r="C26" t="inlineStr">
         <is>
-          <t>303679</t>
+          <t>303678</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1063,13 +1063,13 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>kk_4832738942</t>
+          <t>kk_4832656308</t>
         </is>
       </c>
       <c r="B27" t="inlineStr"/>
       <c r="C27" t="inlineStr">
         <is>
-          <t>303683</t>
+          <t>303679</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1087,13 +1087,13 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>kk_4833682381</t>
+          <t>arumabc</t>
         </is>
       </c>
       <c r="B28" t="inlineStr"/>
       <c r="C28" t="inlineStr">
         <is>
-          <t>303739</t>
+          <t>303689</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1111,13 +1111,13 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>whitehole147</t>
+          <t>kk_4833682381</t>
         </is>
       </c>
       <c r="B29" t="inlineStr"/>
       <c r="C29" t="inlineStr">
         <is>
-          <t>303673</t>
+          <t>303739</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1135,13 +1135,13 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>kk_4833013784</t>
+          <t>kk_4832738942</t>
         </is>
       </c>
       <c r="B30" t="inlineStr"/>
       <c r="C30" t="inlineStr">
         <is>
-          <t>303703</t>
+          <t>303683</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1159,13 +1159,13 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>kk_4833797203</t>
+          <t>kk_4833013784</t>
         </is>
       </c>
       <c r="B31" t="inlineStr"/>
       <c r="C31" t="inlineStr">
         <is>
-          <t>303750</t>
+          <t>303703</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1183,13 +1183,13 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>kk_4832648970</t>
+          <t>kk_4833797203</t>
         </is>
       </c>
       <c r="B32" t="inlineStr"/>
       <c r="C32" t="inlineStr">
         <is>
-          <t>303678</t>
+          <t>303750</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1207,13 +1207,13 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>arumabc</t>
+          <t>whitehole147</t>
         </is>
       </c>
       <c r="B33" t="inlineStr"/>
       <c r="C33" t="inlineStr">
         <is>
-          <t>303689</t>
+          <t>303673</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1255,13 +1255,13 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>kk_4833617385</t>
+          <t>lily50</t>
         </is>
       </c>
       <c r="B35" t="inlineStr"/>
       <c r="C35" t="inlineStr">
         <is>
-          <t>303734</t>
+          <t>303714</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1303,13 +1303,13 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>lily50</t>
+          <t>kk_4833617385</t>
         </is>
       </c>
       <c r="B37" t="inlineStr"/>
       <c r="C37" t="inlineStr">
         <is>
-          <t>303714</t>
+          <t>303734</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1351,13 +1351,13 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>kk_4833397488</t>
+          <t>kk_4832564458</t>
         </is>
       </c>
       <c r="B39" t="inlineStr"/>
       <c r="C39" t="inlineStr">
         <is>
-          <t>303723</t>
+          <t>303676</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1375,13 +1375,13 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>kk_4833698569</t>
+          <t>kk_4833397488</t>
         </is>
       </c>
       <c r="B40" t="inlineStr"/>
       <c r="C40" t="inlineStr">
         <is>
-          <t>303743</t>
+          <t>303723</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -1399,13 +1399,13 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>kk_4833115356</t>
+          <t>kk_4833867742</t>
         </is>
       </c>
       <c r="B41" t="inlineStr"/>
       <c r="C41" t="inlineStr">
         <is>
-          <t>303707</t>
+          <t>303760</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -1447,13 +1447,13 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>kk_4832345614</t>
+          <t>ckddbs4958</t>
         </is>
       </c>
       <c r="B43" t="inlineStr"/>
       <c r="C43" t="inlineStr">
         <is>
-          <t>303664</t>
+          <t>303722</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -1471,13 +1471,13 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>kk_4832562814</t>
+          <t>kk_4833115356</t>
         </is>
       </c>
       <c r="B44" t="inlineStr"/>
       <c r="C44" t="inlineStr">
         <is>
-          <t>303675</t>
+          <t>303707</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -1495,13 +1495,13 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>kk_4833867742</t>
+          <t>kk_4832735078</t>
         </is>
       </c>
       <c r="B45" t="inlineStr"/>
       <c r="C45" t="inlineStr">
         <is>
-          <t>303760</t>
+          <t>303682</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -1519,13 +1519,13 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>kk_4832564458</t>
+          <t>kk_4832986577</t>
         </is>
       </c>
       <c r="B46" t="inlineStr"/>
       <c r="C46" t="inlineStr">
         <is>
-          <t>303676</t>
+          <t>303701</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -1543,13 +1543,13 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>kk_4832425261</t>
+          <t>kk_4833698569</t>
         </is>
       </c>
       <c r="B47" t="inlineStr"/>
       <c r="C47" t="inlineStr">
         <is>
-          <t>303667</t>
+          <t>303743</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -1567,13 +1567,13 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>kk_4832735078</t>
+          <t>kk_4832345614</t>
         </is>
       </c>
       <c r="B48" t="inlineStr"/>
       <c r="C48" t="inlineStr">
         <is>
-          <t>303682</t>
+          <t>303664</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -1591,13 +1591,13 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>kk_4832986577</t>
+          <t>wngml5609</t>
         </is>
       </c>
       <c r="B49" t="inlineStr"/>
       <c r="C49" t="inlineStr">
         <is>
-          <t>303701</t>
+          <t>303704</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -1615,13 +1615,13 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>wngml5609</t>
+          <t>kk_4832425261</t>
         </is>
       </c>
       <c r="B50" t="inlineStr"/>
       <c r="C50" t="inlineStr">
         <is>
-          <t>303704</t>
+          <t>303667</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -1663,13 +1663,13 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>ckddbs4958</t>
+          <t>kk_4832562814</t>
         </is>
       </c>
       <c r="B52" t="inlineStr"/>
       <c r="C52" t="inlineStr">
         <is>
-          <t>303722</t>
+          <t>303675</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -1687,13 +1687,13 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>kk_4833234218</t>
+          <t>kk_4832874454</t>
         </is>
       </c>
       <c r="B53" t="inlineStr"/>
       <c r="C53" t="inlineStr">
         <is>
-          <t>303711</t>
+          <t>303691</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -1759,13 +1759,13 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>kk_4832874454</t>
+          <t>kk_4833234218</t>
         </is>
       </c>
       <c r="B56" t="inlineStr"/>
       <c r="C56" t="inlineStr">
         <is>
-          <t>303691</t>
+          <t>303711</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -1831,13 +1831,13 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>kk_4833289287</t>
+          <t>kk_4833937502</t>
         </is>
       </c>
       <c r="B59" t="inlineStr"/>
       <c r="C59" t="inlineStr">
         <is>
-          <t>303716</t>
+          <t>303767</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -1855,13 +1855,13 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>kk_4833588305</t>
+          <t>kk_4833289287</t>
         </is>
       </c>
       <c r="B60" t="inlineStr"/>
       <c r="C60" t="inlineStr">
         <is>
-          <t>303733</t>
+          <t>303716</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -1879,13 +1879,13 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>kk_4833858368</t>
+          <t>kk_4832497383</t>
         </is>
       </c>
       <c r="B61" t="inlineStr"/>
       <c r="C61" t="inlineStr">
         <is>
-          <t>303758</t>
+          <t>303669</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -1903,13 +1903,13 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>kk_4833937502</t>
+          <t>kk_4833858368</t>
         </is>
       </c>
       <c r="B62" t="inlineStr"/>
       <c r="C62" t="inlineStr">
         <is>
-          <t>303767</t>
+          <t>303758</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -1951,13 +1951,13 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>kk_4832497383</t>
+          <t>kk_4833588305</t>
         </is>
       </c>
       <c r="B64" t="inlineStr"/>
       <c r="C64" t="inlineStr">
         <is>
-          <t>303669</t>
+          <t>303733</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -1999,13 +1999,13 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>hlpt10</t>
+          <t>kk_4832855902</t>
         </is>
       </c>
       <c r="B66" t="inlineStr"/>
       <c r="C66" t="inlineStr">
         <is>
-          <t>303715</t>
+          <t>303690</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -2023,13 +2023,13 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>kk_4832855902</t>
+          <t>kk_4832888908</t>
         </is>
       </c>
       <c r="B67" t="inlineStr"/>
       <c r="C67" t="inlineStr">
         <is>
-          <t>303690</t>
+          <t>303693</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -2071,13 +2071,13 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>kk_4832888908</t>
+          <t>mystyle1999</t>
         </is>
       </c>
       <c r="B69" t="inlineStr"/>
       <c r="C69" t="inlineStr">
         <is>
-          <t>303693</t>
+          <t>303695</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -2095,13 +2095,13 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>mystyle1999</t>
+          <t>hlpt10</t>
         </is>
       </c>
       <c r="B70" t="inlineStr"/>
       <c r="C70" t="inlineStr">
         <is>
-          <t>303695</t>
+          <t>303715</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -2119,13 +2119,13 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>kk_4832527479</t>
+          <t>kk_4832745335</t>
         </is>
       </c>
       <c r="B71" t="inlineStr"/>
       <c r="C71" t="inlineStr">
         <is>
-          <t>303672</t>
+          <t>303684</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -2143,13 +2143,13 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>kk_4832745335</t>
+          <t>kk_4832527479</t>
         </is>
       </c>
       <c r="B72" t="inlineStr"/>
       <c r="C72" t="inlineStr">
         <is>
-          <t>303684</t>
+          <t>303672</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -2263,13 +2263,13 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>hotsnoopy</t>
+          <t>kk_4831402433</t>
         </is>
       </c>
       <c r="B77" t="inlineStr"/>
       <c r="C77" t="inlineStr">
         <is>
-          <t>303585</t>
+          <t>303576</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -2287,13 +2287,13 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>thdud9181</t>
+          <t>kk_4833294708</t>
         </is>
       </c>
       <c r="B78" t="inlineStr"/>
       <c r="C78" t="inlineStr">
         <is>
-          <t>303644</t>
+          <t>303717</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -2311,13 +2311,13 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>kk_4831402433</t>
+          <t>kk_4833232918</t>
         </is>
       </c>
       <c r="B79" t="inlineStr"/>
       <c r="C79" t="inlineStr">
         <is>
-          <t>303576</t>
+          <t>303710</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -2335,13 +2335,13 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>kk_4833961109</t>
+          <t>kk_4832310183</t>
         </is>
       </c>
       <c r="B80" t="inlineStr"/>
       <c r="C80" t="inlineStr">
         <is>
-          <t>303770</t>
+          <t>303663</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -2359,13 +2359,13 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>kk_4833294708</t>
+          <t>thdud9181</t>
         </is>
       </c>
       <c r="B81" t="inlineStr"/>
       <c r="C81" t="inlineStr">
         <is>
-          <t>303717</t>
+          <t>303644</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -2383,13 +2383,13 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>kk_4831784738</t>
+          <t>pjj1758</t>
         </is>
       </c>
       <c r="B82" t="inlineStr"/>
       <c r="C82" t="inlineStr">
         <is>
-          <t>303607</t>
+          <t>303708</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -2407,13 +2407,13 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>kk_4833706874</t>
+          <t>kk_4831784738</t>
         </is>
       </c>
       <c r="B83" t="inlineStr"/>
       <c r="C83" t="inlineStr">
         <is>
-          <t>303744</t>
+          <t>303607</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -2431,13 +2431,13 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>kk_4832310183</t>
+          <t>hotsnoopy</t>
         </is>
       </c>
       <c r="B84" t="inlineStr"/>
       <c r="C84" t="inlineStr">
         <is>
-          <t>303663</t>
+          <t>303585</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -2455,13 +2455,13 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>kk_4833232918</t>
+          <t>kk_4833706874</t>
         </is>
       </c>
       <c r="B85" t="inlineStr"/>
       <c r="C85" t="inlineStr">
         <is>
-          <t>303710</t>
+          <t>303744</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -2479,13 +2479,13 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>pjj1758</t>
+          <t>kk_4833961109</t>
         </is>
       </c>
       <c r="B86" t="inlineStr"/>
       <c r="C86" t="inlineStr">
         <is>
-          <t>303708</t>
+          <t>303770</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -2527,13 +2527,13 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>kk_4830612400</t>
+          <t>kk_4831842028</t>
         </is>
       </c>
       <c r="B88" t="inlineStr"/>
       <c r="C88" t="inlineStr">
         <is>
-          <t>303542</t>
+          <t>303612</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -2551,13 +2551,13 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>kk_4831842028</t>
+          <t>kk_4830612400</t>
         </is>
       </c>
       <c r="B89" t="inlineStr"/>
       <c r="C89" t="inlineStr">
         <is>
-          <t>303612</t>
+          <t>303542</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -2767,13 +2767,13 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>kk_4831995357</t>
+          <t>kk_4831768959</t>
         </is>
       </c>
       <c r="B98" t="inlineStr"/>
       <c r="C98" t="inlineStr">
         <is>
-          <t>303623</t>
+          <t>303602</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -2791,13 +2791,13 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>kk_4831768959</t>
+          <t>kk_4830251299</t>
         </is>
       </c>
       <c r="B99" t="inlineStr"/>
       <c r="C99" t="inlineStr">
         <is>
-          <t>303602</t>
+          <t>303511</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -2839,13 +2839,13 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>kk_4830251299</t>
+          <t>kk_4831995357</t>
         </is>
       </c>
       <c r="B101" t="inlineStr"/>
       <c r="C101" t="inlineStr">
         <is>
-          <t>303511</t>
+          <t>303623</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -2863,13 +2863,13 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>kk_4832105165</t>
+          <t>kk_4831842112</t>
         </is>
       </c>
       <c r="B102" t="inlineStr"/>
       <c r="C102" t="inlineStr">
         <is>
-          <t>303636</t>
+          <t>303613</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -2887,13 +2887,13 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>kk_4831842112</t>
+          <t>kk_4832105165</t>
         </is>
       </c>
       <c r="B103" t="inlineStr"/>
       <c r="C103" t="inlineStr">
         <is>
-          <t>303613</t>
+          <t>303636</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -2911,13 +2911,13 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>kk_4830767555</t>
+          <t>kk_4832023314</t>
         </is>
       </c>
       <c r="B104" t="inlineStr"/>
       <c r="C104" t="inlineStr">
         <is>
-          <t>303555</t>
+          <t>303626</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -2935,13 +2935,13 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>kk_4832248726</t>
+          <t>kk_4831394790</t>
         </is>
       </c>
       <c r="B105" t="inlineStr"/>
       <c r="C105" t="inlineStr">
         <is>
-          <t>303658</t>
+          <t>303575</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -2959,13 +2959,13 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>kk_4831346086</t>
+          <t>kk_4830767555</t>
         </is>
       </c>
       <c r="B106" t="inlineStr"/>
       <c r="C106" t="inlineStr">
         <is>
-          <t>303573</t>
+          <t>303555</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -2983,13 +2983,13 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>kk_4832180009</t>
+          <t>kk_4832248726</t>
         </is>
       </c>
       <c r="B107" t="inlineStr"/>
       <c r="C107" t="inlineStr">
         <is>
-          <t>303647</t>
+          <t>303658</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -3007,13 +3007,13 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>kk_4831394790</t>
+          <t>kk_4832201164</t>
         </is>
       </c>
       <c r="B108" t="inlineStr"/>
       <c r="C108" t="inlineStr">
         <is>
-          <t>303575</t>
+          <t>303651</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -3031,13 +3031,13 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>kk_4832023314</t>
+          <t>kk_4832180009</t>
         </is>
       </c>
       <c r="B109" t="inlineStr"/>
       <c r="C109" t="inlineStr">
         <is>
-          <t>303626</t>
+          <t>303647</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -3079,13 +3079,13 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>kk_4832114535</t>
+          <t>kk_4831346086</t>
         </is>
       </c>
       <c r="B111" t="inlineStr"/>
       <c r="C111" t="inlineStr">
         <is>
-          <t>303637</t>
+          <t>303573</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -3127,13 +3127,13 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>kk_4832201164</t>
+          <t>kk_4832114535</t>
         </is>
       </c>
       <c r="B113" t="inlineStr"/>
       <c r="C113" t="inlineStr">
         <is>
-          <t>303651</t>
+          <t>303637</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -3223,13 +3223,13 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>kk_4832078505</t>
+          <t>kk_4832100095</t>
         </is>
       </c>
       <c r="B117" t="inlineStr"/>
       <c r="C117" t="inlineStr">
         <is>
-          <t>303630</t>
+          <t>303634</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -3247,13 +3247,13 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>kk_4831340465</t>
+          <t>jambo8</t>
         </is>
       </c>
       <c r="B118" t="inlineStr"/>
       <c r="C118" t="inlineStr">
         <is>
-          <t>303572</t>
+          <t>303558</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -3271,13 +3271,13 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>kk_4832100095</t>
+          <t>kk_4832029124</t>
         </is>
       </c>
       <c r="B119" t="inlineStr"/>
       <c r="C119" t="inlineStr">
         <is>
-          <t>303634</t>
+          <t>303627</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -3295,13 +3295,13 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>kk_4832029124</t>
+          <t>kk_4832078505</t>
         </is>
       </c>
       <c r="B120" t="inlineStr"/>
       <c r="C120" t="inlineStr">
         <is>
-          <t>303627</t>
+          <t>303630</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -3319,13 +3319,13 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>jambo8</t>
+          <t>kk_4831340465</t>
         </is>
       </c>
       <c r="B121" t="inlineStr"/>
       <c r="C121" t="inlineStr">
         <is>
-          <t>303558</t>
+          <t>303572</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -3391,13 +3391,13 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>kk_4831830576</t>
+          <t>jgj0503</t>
         </is>
       </c>
       <c r="B124" t="inlineStr"/>
       <c r="C124" t="inlineStr">
         <is>
-          <t>303611</t>
+          <t>303605</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -3439,13 +3439,13 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>jgj0503</t>
+          <t>kk_4830989652</t>
         </is>
       </c>
       <c r="B126" t="inlineStr"/>
       <c r="C126" t="inlineStr">
         <is>
-          <t>303605</t>
+          <t>303569</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -3463,13 +3463,13 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>kk_4830989652</t>
+          <t>kk_4831830576</t>
         </is>
       </c>
       <c r="B127" t="inlineStr"/>
       <c r="C127" t="inlineStr">
         <is>
-          <t>303569</t>
+          <t>303611</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -3511,13 +3511,13 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>kk_4831922723</t>
+          <t>kk_4831850638</t>
         </is>
       </c>
       <c r="B129" t="inlineStr"/>
       <c r="C129" t="inlineStr">
         <is>
-          <t>303617</t>
+          <t>303615</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -3559,13 +3559,13 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>kk_4830836853</t>
+          <t>kk_4830778741</t>
         </is>
       </c>
       <c r="B131" t="inlineStr"/>
       <c r="C131" t="inlineStr">
         <is>
-          <t>303560</t>
+          <t>303556</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -3583,13 +3583,13 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>kk_4831850638</t>
+          <t>kk_4831922723</t>
         </is>
       </c>
       <c r="B132" t="inlineStr"/>
       <c r="C132" t="inlineStr">
         <is>
-          <t>303615</t>
+          <t>303617</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -3607,13 +3607,13 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>kk_4830778741</t>
+          <t>kk_4830836853</t>
         </is>
       </c>
       <c r="B133" t="inlineStr"/>
       <c r="C133" t="inlineStr">
         <is>
-          <t>303556</t>
+          <t>303560</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -3703,13 +3703,13 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>kk_4831532519</t>
+          <t>kk_4832001343</t>
         </is>
       </c>
       <c r="B137" t="inlineStr"/>
       <c r="C137" t="inlineStr">
         <is>
-          <t>303587</t>
+          <t>303625</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -3727,13 +3727,13 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>kk_4831986570</t>
+          <t>kk_4832061430</t>
         </is>
       </c>
       <c r="B138" t="inlineStr"/>
       <c r="C138" t="inlineStr">
         <is>
-          <t>303622</t>
+          <t>303628</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -3751,13 +3751,13 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>kk_4832100101</t>
+          <t>kk_4832190692</t>
         </is>
       </c>
       <c r="B139" t="inlineStr"/>
       <c r="C139" t="inlineStr">
         <is>
-          <t>303635</t>
+          <t>303649</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -3775,13 +3775,13 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>kk_4831981914</t>
+          <t>kk_4831983348</t>
         </is>
       </c>
       <c r="B140" t="inlineStr"/>
       <c r="C140" t="inlineStr">
         <is>
-          <t>303620</t>
+          <t>303621</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -3799,13 +3799,13 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>kk_4831799020</t>
+          <t>kk_4831997957</t>
         </is>
       </c>
       <c r="B141" t="inlineStr"/>
       <c r="C141" t="inlineStr">
         <is>
-          <t>303609</t>
+          <t>303624</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -3823,13 +3823,13 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>kk_4831983348</t>
+          <t>kk_4831799020</t>
         </is>
       </c>
       <c r="B142" t="inlineStr"/>
       <c r="C142" t="inlineStr">
         <is>
-          <t>303621</t>
+          <t>303609</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -3847,13 +3847,13 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>kk_4832061430</t>
+          <t>kk_4831981914</t>
         </is>
       </c>
       <c r="B143" t="inlineStr"/>
       <c r="C143" t="inlineStr">
         <is>
-          <t>303628</t>
+          <t>303620</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -3871,13 +3871,13 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>kk_4832001343</t>
+          <t>kk_4831502482</t>
         </is>
       </c>
       <c r="B144" t="inlineStr"/>
       <c r="C144" t="inlineStr">
         <is>
-          <t>303625</t>
+          <t>303583</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -3895,13 +3895,13 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>kk_4831502482</t>
+          <t>kk_4831986570</t>
         </is>
       </c>
       <c r="B145" t="inlineStr"/>
       <c r="C145" t="inlineStr">
         <is>
-          <t>303583</t>
+          <t>303622</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -3919,13 +3919,13 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>kk_4831257396</t>
+          <t>kk_4831532519</t>
         </is>
       </c>
       <c r="B146" t="inlineStr"/>
       <c r="C146" t="inlineStr">
         <is>
-          <t>303571</t>
+          <t>303587</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -3943,13 +3943,13 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>kk_4832190692</t>
+          <t>kk_4832100101</t>
         </is>
       </c>
       <c r="B147" t="inlineStr"/>
       <c r="C147" t="inlineStr">
         <is>
-          <t>303649</t>
+          <t>303635</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -3967,13 +3967,13 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>kk_4831997957</t>
+          <t>kk_4831257396</t>
         </is>
       </c>
       <c r="B148" t="inlineStr"/>
       <c r="C148" t="inlineStr">
         <is>
-          <t>303624</t>
+          <t>303571</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -3991,13 +3991,13 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>kk_4832186210</t>
+          <t>kk_4831774426</t>
         </is>
       </c>
       <c r="B149" t="inlineStr"/>
       <c r="C149" t="inlineStr">
         <is>
-          <t>303648</t>
+          <t>303604</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -4015,13 +4015,13 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>kk_4831774426</t>
+          <t>kk_4832186210</t>
         </is>
       </c>
       <c r="B150" t="inlineStr"/>
       <c r="C150" t="inlineStr">
         <is>
-          <t>303604</t>
+          <t>303648</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -4039,13 +4039,13 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>kk_4831822425</t>
+          <t>kk_4831585022</t>
         </is>
       </c>
       <c r="B151" t="inlineStr"/>
       <c r="C151" t="inlineStr">
         <is>
-          <t>303610</t>
+          <t>303591</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -4087,13 +4087,13 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>kk_4831951614</t>
+          <t>kk_4831822425</t>
         </is>
       </c>
       <c r="B153" t="inlineStr"/>
       <c r="C153" t="inlineStr">
         <is>
-          <t>303618</t>
+          <t>303610</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -4111,13 +4111,13 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>kk_4831585022</t>
+          <t>kk_4831951614</t>
         </is>
       </c>
       <c r="B154" t="inlineStr"/>
       <c r="C154" t="inlineStr">
         <is>
-          <t>303591</t>
+          <t>303618</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -4159,13 +4159,13 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>minpark98</t>
+          <t>kk_4831488942</t>
         </is>
       </c>
       <c r="B156" t="inlineStr"/>
       <c r="C156" t="inlineStr">
         <is>
-          <t>303657</t>
+          <t>303580</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -4183,13 +4183,13 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>kk_4831488942</t>
+          <t>minpark98</t>
         </is>
       </c>
       <c r="B157" t="inlineStr"/>
       <c r="C157" t="inlineStr">
         <is>
-          <t>303580</t>
+          <t>303657</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -4207,13 +4207,13 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>kk_4831615271</t>
+          <t>kk_4831600231</t>
         </is>
       </c>
       <c r="B158" t="inlineStr"/>
       <c r="C158" t="inlineStr">
         <is>
-          <t>303594</t>
+          <t>303592</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -4231,13 +4231,13 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>kk_4831600231</t>
+          <t>kk_4831615271</t>
         </is>
       </c>
       <c r="B159" t="inlineStr"/>
       <c r="C159" t="inlineStr">
         <is>
-          <t>303592</t>
+          <t>303594</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -4279,13 +4279,13 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>kk_4830147171</t>
+          <t>kk_4830615705</t>
         </is>
       </c>
       <c r="B161" t="inlineStr"/>
       <c r="C161" t="inlineStr">
         <is>
-          <t>303506</t>
+          <t>303543</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -4303,13 +4303,13 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>kk_4830615705</t>
+          <t>kk_4830147171</t>
         </is>
       </c>
       <c r="B162" t="inlineStr"/>
       <c r="C162" t="inlineStr">
         <is>
-          <t>303543</t>
+          <t>303506</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -4399,13 +4399,13 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>kk_4830179868</t>
+          <t>kk_4830596422</t>
         </is>
       </c>
       <c r="B166" t="inlineStr"/>
       <c r="C166" t="inlineStr">
         <is>
-          <t>303508</t>
+          <t>303540</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -4423,13 +4423,13 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>kk_4830596422</t>
+          <t>kk_4830179868</t>
         </is>
       </c>
       <c r="B167" t="inlineStr"/>
       <c r="C167" t="inlineStr">
         <is>
-          <t>303540</t>
+          <t>303508</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -4495,13 +4495,13 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>kk_4829999849</t>
+          <t>kk_4830404781</t>
         </is>
       </c>
       <c r="B170" t="inlineStr"/>
       <c r="C170" t="inlineStr">
         <is>
-          <t>303498</t>
+          <t>303521</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -4519,13 +4519,13 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>kk_4830692253</t>
+          <t>kk_4830541132</t>
         </is>
       </c>
       <c r="B171" t="inlineStr"/>
       <c r="C171" t="inlineStr">
         <is>
-          <t>303550</t>
+          <t>303533</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -4543,13 +4543,13 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>kk_4830409260</t>
+          <t>kk_4829999849</t>
         </is>
       </c>
       <c r="B172" t="inlineStr"/>
       <c r="C172" t="inlineStr">
         <is>
-          <t>303522</t>
+          <t>303498</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -4567,13 +4567,13 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>kk_4830404781</t>
+          <t>kk_4830692253</t>
         </is>
       </c>
       <c r="B173" t="inlineStr"/>
       <c r="C173" t="inlineStr">
         <is>
-          <t>303521</t>
+          <t>303550</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -4615,13 +4615,13 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>kk_4830541132</t>
+          <t>kk_4830409260</t>
         </is>
       </c>
       <c r="B175" t="inlineStr"/>
       <c r="C175" t="inlineStr">
         <is>
-          <t>303533</t>
+          <t>303522</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -4639,13 +4639,13 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>kk_4830559393</t>
+          <t>mong81</t>
         </is>
       </c>
       <c r="B176" t="inlineStr"/>
       <c r="C176" t="inlineStr">
         <is>
-          <t>303535</t>
+          <t>303505</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -4663,13 +4663,13 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>mong81</t>
+          <t>kk_4830559393</t>
         </is>
       </c>
       <c r="B177" t="inlineStr"/>
       <c r="C177" t="inlineStr">
         <is>
-          <t>303505</t>
+          <t>303535</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -4735,13 +4735,13 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>kk_4830704540</t>
+          <t>flydabi</t>
         </is>
       </c>
       <c r="B180" t="inlineStr"/>
       <c r="C180" t="inlineStr">
         <is>
-          <t>303551</t>
+          <t>303531</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -4807,13 +4807,13 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>kk_4830597347</t>
+          <t>kk_4830376206</t>
         </is>
       </c>
       <c r="B183" t="inlineStr"/>
       <c r="C183" t="inlineStr">
         <is>
-          <t>303541</t>
+          <t>303520</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -4831,13 +4831,13 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>flydabi</t>
+          <t>kk_4830308577</t>
         </is>
       </c>
       <c r="B184" t="inlineStr"/>
       <c r="C184" t="inlineStr">
         <is>
-          <t>303531</t>
+          <t>303516</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -4855,13 +4855,13 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>kk_4830376206</t>
+          <t>kk_4830704540</t>
         </is>
       </c>
       <c r="B185" t="inlineStr"/>
       <c r="C185" t="inlineStr">
         <is>
-          <t>303520</t>
+          <t>303551</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -4879,13 +4879,13 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>kk_4830308577</t>
+          <t>kk_4830722522</t>
         </is>
       </c>
       <c r="B186" t="inlineStr"/>
       <c r="C186" t="inlineStr">
         <is>
-          <t>303516</t>
+          <t>303553</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -4927,13 +4927,13 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>kk_4830722522</t>
+          <t>kk_4830597347</t>
         </is>
       </c>
       <c r="B188" t="inlineStr"/>
       <c r="C188" t="inlineStr">
         <is>
-          <t>303553</t>
+          <t>303541</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
